--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28T05:02:20+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-28T05:51:53+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28T08:09:25+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-28T19:31:40+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4530000374242298</v>
+        <v>0.456769801952032</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>38.970916</v>
+        <v>39.295223</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.852811</v>
+        <v>0.845773</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005869829746987211</v>
+        <v>0.005918677151261723</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.48561407492389</v>
+        <v>38.73601729148395</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>52.6172979768608</v>
+        <v>52.99042053631734</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.503458</v>
+        <v>12.420349</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.489435</v>
+        <v>50.843777</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>47.888092</v>
+        <v>48.220373</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.28675</v>
+        <v>45.596968</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>42.685407</v>
+        <v>42.973564</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.084065</v>
+        <v>40.350159</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>50.714576</v>
+        <v>51.070462</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.101635</v>
+        <v>48.435363</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.488694</v>
+        <v>45.800264</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>42.875753</v>
+        <v>43.165164</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.262812</v>
+        <v>40.530065</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>50.939717</v>
+        <v>51.297148</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.315177</v>
+        <v>48.650353</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>45.690638</v>
+        <v>46.003559</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.066098</v>
+        <v>43.356765</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.441559</v>
+        <v>40.70997</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.164858</v>
+        <v>51.523833</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.52872</v>
+        <v>48.865344</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>45.892582</v>
+        <v>46.206854</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.256444</v>
+        <v>43.548365</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.620306</v>
+        <v>40.889876</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.389999</v>
+        <v>51.750519</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>48.742263</v>
+        <v>49.080334</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.094526</v>
+        <v>46.41015</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.44679</v>
+        <v>43.739965</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>40.799053</v>
+        <v>41.069781</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2968379581889223</v>
+        <v>0.2993081769810631</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>207.101805</v>
+        <v>208.061435</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>199.5421109785326</v>
+        <v>200.487400843962</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>266.0561479713768</v>
+        <v>267.316534458616</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.621407</v>
+        <v>3.604705</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>263.68927</v>
+        <v>264.938689</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>247.208691</v>
+        <v>248.380021</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>230.728111</v>
+        <v>231.821353</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>214.247532</v>
+        <v>215.262685</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>197.766953</v>
+        <v>198.704017</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>264.872709</v>
+        <v>266.127612</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>248.318165</v>
+        <v>249.494636</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>231.76362</v>
+        <v>232.86166</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>215.209076</v>
+        <v>216.228685</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>198.654532</v>
+        <v>199.595709</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>266.056148</v>
+        <v>267.316534</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>249.427639</v>
+        <v>250.609251</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>232.799129</v>
+        <v>233.901968</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>216.17062</v>
+        <v>217.194684</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>199.542111</v>
+        <v>200.487401</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>267.239587</v>
+        <v>268.505457</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>250.537113</v>
+        <v>251.723866</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>233.834639</v>
+        <v>234.942275</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>217.132164</v>
+        <v>218.160684</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>200.42969</v>
+        <v>201.379093</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>268.423026</v>
+        <v>269.694379</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>251.646587</v>
+        <v>252.838481</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>234.870148</v>
+        <v>235.982582</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>218.093708</v>
+        <v>219.126683</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>201.317269</v>
+        <v>202.270785</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.665496301645546</v>
+        <v>1.679356187650918</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>149.243494</v>
+        <v>150.485465</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.852811</v>
+        <v>0.845773</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.542483</v>
+        <v>15.445123</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.0895474785341</v>
+        <v>289.643969088786</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>319.4932113051718</v>
+        <v>320.3174373057688</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>316.804685</v>
+        <v>317.623451</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>309.26773</v>
+        <v>310.019577</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>301.730776</v>
+        <v>302.415704</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.193821</v>
+        <v>294.811831</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>286.656867</v>
+        <v>287.207957</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>318.148948</v>
+        <v>318.970444</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>310.580013</v>
+        <v>311.334324</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.011078</v>
+        <v>303.698204</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>295.442142</v>
+        <v>296.062083</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>287.873207</v>
+        <v>288.425963</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>319.493211</v>
+        <v>320.317437</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>311.892295</v>
+        <v>312.64907</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>304.291379</v>
+        <v>304.980703</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>296.690463</v>
+        <v>297.312336</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.089547</v>
+        <v>289.643969</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>320.837475</v>
+        <v>321.664431</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>313.204578</v>
+        <v>313.963817</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>305.571681</v>
+        <v>306.263203</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>297.938784</v>
+        <v>298.562589</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.305888</v>
+        <v>290.861975</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>322.181738</v>
+        <v>323.011424</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>314.51686</v>
+        <v>315.278563</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>306.851983</v>
+        <v>307.545702</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.187105</v>
+        <v>299.812842</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>291.522228</v>
+        <v>292.079981</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.193583</v>
+        <v>5.15072</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.93347</v>
+        <v>3.920874</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.040877</v>
+        <v>0.041218</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.379897</v>
+        <v>8.310737</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.446031</v>
+        <v>4.407594</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.119285</v>
+        <v>0.120278</v>
       </c>
     </row>
     <row r="4">
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>85.07890999999999</v>
+        <v>84.376745</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>15.104914</v>
+        <v>15.055741</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.011754</v>
+        <v>0.011852</v>
       </c>
     </row>
     <row r="8">
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1720.663194</v>
+        <v>1706.462397</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.480343</v>
+        <v>14.397445</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.2e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>39.176252</v>
+        <v>38.852927</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.766212</v>
+        <v>15.665386</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.75277</v>
+        <v>10.716527</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2540.001335</v>
+        <v>2547.860407</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>103.8285183893187</v>
+        <v>104.6925559903393</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2527.993082784294</v>
+        <v>2542.279703015659</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3615.278062230801</v>
+        <v>3632.928874082497</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3584.390207</v>
+        <v>3601.88725</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3314.826487</v>
+        <v>3331.489467</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3045.262767</v>
+        <v>3061.091684</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2775.699047</v>
+        <v>2790.693901</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2506.135327</v>
+        <v>2520.296118</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3599.834135</v>
+        <v>3617.408062</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3329.141652</v>
+        <v>3345.878024</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3058.44917</v>
+        <v>3074.347986</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2787.756687</v>
+        <v>2802.817948</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2517.064205</v>
+        <v>2531.28791</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3615.278062</v>
+        <v>3632.928874</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3343.456817</v>
+        <v>3360.266581</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3071.635573</v>
+        <v>3087.604289</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2799.814328</v>
+        <v>2814.941996</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2527.993083</v>
+        <v>2542.279703</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3630.72199</v>
+        <v>3648.449686</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3357.771983</v>
+        <v>3374.655139</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3084.821975</v>
+        <v>3100.860591</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2811.871968</v>
+        <v>2827.066043</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2538.921961</v>
+        <v>2553.271496</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3646.165918</v>
+        <v>3663.970499</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3372.087148</v>
+        <v>3389.043696</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3098.008378</v>
+        <v>3114.116893</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2823.929609</v>
+        <v>2839.190091</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2549.850839</v>
+        <v>2564.263288</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4934065725192069</v>
+        <v>0.4975125911532087</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2379.342963</v>
+        <v>2389.971001</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>293.4422798762812</v>
+        <v>295.8842405964722</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1865.688134798716</v>
+        <v>1876.236198792732</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2313.417703343997</v>
+        <v>2325.988660683207</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2297.618536</v>
+        <v>2310.120912</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2183.072318</v>
+        <v>2195.043288</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2068.5261</v>
+        <v>2079.965664</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1953.979881</v>
+        <v>1964.88804</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1839.433663</v>
+        <v>1849.810415</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2309.151664</v>
+        <v>2321.718568</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2194.095587</v>
+        <v>2206.128808</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2079.039509</v>
+        <v>2090.539047</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1963.983432</v>
+        <v>1974.949286</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1848.927355</v>
+        <v>1859.359525</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2320.684792</v>
+        <v>2333.316225</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2205.118856</v>
+        <v>2217.214327</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2089.552919</v>
+        <v>2101.11243</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1973.986982</v>
+        <v>1985.010532</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1858.421046</v>
+        <v>1868.908635</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2332.21792</v>
+        <v>2344.913881</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2216.142125</v>
+        <v>2228.299847</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2100.066329</v>
+        <v>2111.685813</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1983.990533</v>
+        <v>1995.071779</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1867.914737</v>
+        <v>1878.457744</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2343.751049</v>
+        <v>2356.511537</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2227.165394</v>
+        <v>2239.385367</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2110.579739</v>
+        <v>2122.259196</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>1993.994083</v>
+        <v>2005.133025</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1877.408428</v>
+        <v>1888.006854</v>
       </c>
     </row>
   </sheetData>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.963795</v>
+        <v>1.947588</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.97459745527777</v>
+        <v>30.84989255641144</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>37.07633612552448</v>
+        <v>36.95163122665815</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.817233</v>
+        <v>1.824009</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.766357</v>
+        <v>36.642694</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.253675</v>
+        <v>35.130013</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.740994</v>
+        <v>33.617332</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.228313</v>
+        <v>32.104651</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.715632</v>
+        <v>30.59197</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.921346</v>
+        <v>36.797163</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.402288</v>
+        <v>35.278105</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.883231</v>
+        <v>33.759047</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.364173</v>
+        <v>32.239989</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.845115</v>
+        <v>30.720931</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>37.076336</v>
+        <v>36.951631</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.550901</v>
+        <v>35.426197</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>34.025467</v>
+        <v>33.900762</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.500032</v>
+        <v>32.375327</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.974597</v>
+        <v>30.849893</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.231326</v>
+        <v>37.1061</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.699514</v>
+        <v>35.574288</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.167703</v>
+        <v>34.042477</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.635892</v>
+        <v>32.510665</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>31.10408</v>
+        <v>30.978854</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.386316</v>
+        <v>37.260568</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.848127</v>
+        <v>35.72238</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.309939</v>
+        <v>34.184192</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.771751</v>
+        <v>32.646004</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.233563</v>
+        <v>31.107815</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18025</v>
+        <v>18175</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.173498381596009</v>
+        <v>1.183263971456725</v>
       </c>
     </row>
     <row r="92">
@@ -51122,7 +51122,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>8.598459</v>
+        <v>8.562229</v>
       </c>
     </row>
     <row r="104">
@@ -51239,7 +51239,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>16.51408090824167</v>
+        <v>16.65150737904534</v>
       </c>
     </row>
     <row r="118">
@@ -51270,7 +51270,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1758.008562157326</v>
+        <v>1762.764775806316</v>
       </c>
     </row>
     <row r="121">
@@ -51300,7 +51300,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2139.768386048682</v>
+        <v>2144.662172895838</v>
       </c>
     </row>
     <row r="124">
@@ -51342,7 +51342,7 @@
         </is>
       </c>
       <c r="C127" s="18" t="n">
-        <v>0.832999</v>
+        <v>0.831228</v>
       </c>
     </row>
     <row r="128">
@@ -51483,19 +51483,19 @@
         <v>-0.01</v>
       </c>
       <c r="D141" s="23" t="n">
-        <v>2122.056522</v>
+        <v>2126.921031</v>
       </c>
       <c r="E141" s="23" t="n">
-        <v>2027.039118</v>
+        <v>2031.865906</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>1932.021714</v>
+        <v>1936.81078</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>1837.004309</v>
+        <v>1841.755654</v>
       </c>
       <c r="H141" s="23" t="n">
-        <v>1741.986905</v>
+        <v>1746.700528</v>
       </c>
     </row>
     <row r="142">
@@ -51503,19 +51503,19 @@
         <v>-0.005</v>
       </c>
       <c r="D142" s="23" t="n">
-        <v>2131.312385</v>
+        <v>2136.194861</v>
       </c>
       <c r="E142" s="23" t="n">
-        <v>2035.883739</v>
+        <v>2040.728494</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>1940.455094</v>
+        <v>1945.262127</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1845.026448</v>
+        <v>1849.79576</v>
       </c>
       <c r="H142" s="23" t="n">
-        <v>1749.597803</v>
+        <v>1754.329393</v>
       </c>
     </row>
     <row r="143">
@@ -51523,19 +51523,19 @@
         <v>0</v>
       </c>
       <c r="D143" s="23" t="n">
-        <v>2140.568247</v>
+        <v>2145.46869</v>
       </c>
       <c r="E143" s="23" t="n">
-        <v>2044.728361</v>
+        <v>2049.591082</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1948.888474</v>
+        <v>1953.713474</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>1853.048588</v>
+        <v>1857.835866</v>
       </c>
       <c r="H143" s="23" t="n">
-        <v>1757.208701</v>
+        <v>1761.958258</v>
       </c>
     </row>
     <row r="144">
@@ -51543,19 +51543,19 @@
         <v>0.005</v>
       </c>
       <c r="D144" s="23" t="n">
-        <v>2149.824109</v>
+        <v>2154.74252</v>
       </c>
       <c r="E144" s="23" t="n">
-        <v>2053.572982</v>
+        <v>2058.453671</v>
       </c>
       <c r="F144" s="23" t="n">
-        <v>1957.321854</v>
+        <v>1962.164822</v>
       </c>
       <c r="G144" s="23" t="n">
-        <v>1861.070727</v>
+        <v>1865.875973</v>
       </c>
       <c r="H144" s="23" t="n">
-        <v>1764.819599</v>
+        <v>1769.587124</v>
       </c>
     </row>
     <row r="145">
@@ -51563,19 +51563,19 @@
         <v>0.01</v>
       </c>
       <c r="D145" s="23" t="n">
-        <v>2159.079972</v>
+        <v>2164.016349</v>
       </c>
       <c r="E145" s="23" t="n">
-        <v>2062.417603</v>
+        <v>2067.316259</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1965.755235</v>
+        <v>1970.616169</v>
       </c>
       <c r="G145" s="23" t="n">
-        <v>1869.092866</v>
+        <v>1873.916079</v>
       </c>
       <c r="H145" s="23" t="n">
-        <v>1772.430498</v>
+        <v>1777.215989</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28T19:31:40+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-28T22:55:13+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -25947,13 +25947,13 @@
         <v/>
       </c>
       <c r="H4" s="9" t="n">
-        <v>5.781403</v>
+        <v>5.483461</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>4.736639</v>
+        <v>5.176372</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08648400000000001</v>
+        <v>0.091183</v>
       </c>
     </row>
     <row r="5">
@@ -34904,7 +34904,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.220925</v>
+        <v>0.2169</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0.220925</v>
@@ -34946,7 +34946,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1112</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0.101353</v>
@@ -35228,7 +35228,7 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>10702</v>
+        <v>13200</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>10702</v>
@@ -35270,7 +35270,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.14</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0.213707</v>
@@ -35354,7 +35354,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.013</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>-0.02</v>
@@ -38630,7 +38630,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>392.6382537228818</v>
+        <v>413.9721525448721</v>
       </c>
     </row>
     <row r="118">
@@ -38661,7 +38661,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>5009.300470800708</v>
+        <v>4992.370830783081</v>
       </c>
     </row>
     <row r="121">
@@ -38691,7 +38691,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>5677.192522546568</v>
+        <v>5651.267349617006</v>
       </c>
     </row>
     <row r="124">
@@ -38782,19 +38782,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>5681.645735</v>
+        <v>5660.311836</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>5487.957627</v>
+        <v>5466.623729</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>5294.26952</v>
+        <v>5272.935621</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>5100.581412</v>
+        <v>5079.247514</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>4906.893305</v>
+        <v>4885.559406</v>
       </c>
     </row>
     <row r="133">
@@ -38802,19 +38802,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>5708.301415</v>
+        <v>5686.967516</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>5513.763349</v>
+        <v>5492.429451</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>5319.225284</v>
+        <v>5297.891385</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>5124.687218</v>
+        <v>5103.353319</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>4930.149152</v>
+        <v>4908.815253</v>
       </c>
     </row>
     <row r="134">
@@ -38822,19 +38822,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>5734.957095</v>
+        <v>5713.623197</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>5539.569071</v>
+        <v>5518.235172</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>5344.181047</v>
+        <v>5322.847148</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>5148.793023</v>
+        <v>5127.459124</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>4953.404999</v>
+        <v>4932.0711</v>
       </c>
     </row>
     <row r="135">
@@ -38842,19 +38842,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>5761.612776</v>
+        <v>5740.278877</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>5565.374793</v>
+        <v>5544.040894</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>5369.136811</v>
+        <v>5347.802912</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>5172.898828</v>
+        <v>5151.564929</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>4976.660846</v>
+        <v>4955.326947</v>
       </c>
     </row>
     <row r="136">
@@ -38862,19 +38862,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>5788.268456</v>
+        <v>5766.934557</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>5591.180515</v>
+        <v>5569.846616</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>5394.092574</v>
+        <v>5372.758675</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>5197.004633</v>
+        <v>5175.670735</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>4999.916693</v>
+        <v>4978.582794</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28T22:55:13+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T02:00:09+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.456769801952032</v>
+        <v>0.4569708560601814</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.295223</v>
+        <v>39.31252</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.845773</v>
+        <v>0.845401</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005918677151261723</v>
+        <v>0.005921282346156363</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.73601729148395</v>
+        <v>38.76384520493933</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>52.99042053631734</v>
+        <v>53.03083191315557</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.420349</v>
+        <v>12.415948</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.843777</v>
+        <v>50.88218</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.220373</v>
+        <v>48.256593</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.596968</v>
+        <v>45.631005</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>42.973564</v>
+        <v>43.005418</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.350159</v>
+        <v>40.379831</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>51.070462</v>
+        <v>51.108948</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.435363</v>
+        <v>48.471661</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.800264</v>
+        <v>45.834373</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.165164</v>
+        <v>43.197085</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.530065</v>
+        <v>40.559798</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.297148</v>
+        <v>51.335716</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.650353</v>
+        <v>48.686728</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>46.003559</v>
+        <v>46.03774</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.356765</v>
+        <v>43.388753</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.70997</v>
+        <v>40.739765</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.523833</v>
+        <v>51.562484</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.865344</v>
+        <v>48.901796</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.206854</v>
+        <v>46.241108</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.548365</v>
+        <v>43.58042</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.889876</v>
+        <v>40.919732</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.750519</v>
+        <v>51.789252</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>49.080334</v>
+        <v>49.116863</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.41015</v>
+        <v>46.444475</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.739965</v>
+        <v>43.772087</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>41.069781</v>
+        <v>41.099699</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2993081769810631</v>
+        <v>0.2994399219833106</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>208.061435</v>
+        <v>208.365312</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>200.487400843962</v>
+        <v>200.858118751518</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>267.316534458616</v>
+        <v>267.8108250020241</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.604705</v>
+        <v>3.599447</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>264.938689</v>
+        <v>265.429507</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>248.380021</v>
+        <v>248.840163</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>231.821353</v>
+        <v>232.250819</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>215.262685</v>
+        <v>215.661475</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>198.704017</v>
+        <v>199.07213</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>266.127612</v>
+        <v>266.620166</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>249.494636</v>
+        <v>249.956406</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>232.86166</v>
+        <v>233.292645</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>216.228685</v>
+        <v>216.628885</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>199.595709</v>
+        <v>199.965125</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>267.316534</v>
+        <v>267.810825</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>250.609251</v>
+        <v>251.072648</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>233.901968</v>
+        <v>234.334472</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>217.194684</v>
+        <v>217.596295</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>200.487401</v>
+        <v>200.858119</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>268.505457</v>
+        <v>269.001484</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>251.723866</v>
+        <v>252.188891</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>234.942275</v>
+        <v>235.376298</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>218.160684</v>
+        <v>218.563706</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>201.379093</v>
+        <v>201.751113</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>269.694379</v>
+        <v>270.192143</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>252.838481</v>
+        <v>253.305134</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>235.982582</v>
+        <v>236.418125</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>219.126683</v>
+        <v>219.531116</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>202.270785</v>
+        <v>202.644107</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.679356187650918</v>
+        <v>1.680095381571204</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.485465</v>
+        <v>150.551704</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.845773</v>
+        <v>0.845401</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.445123</v>
+        <v>15.439976</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.643969088786</v>
+        <v>289.7783065641057</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.3174373057688</v>
+        <v>320.4772699452854</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.623451</v>
+        <v>317.782992</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>310.019577</v>
+        <v>310.172773</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.415704</v>
+        <v>302.562555</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.811831</v>
+        <v>294.952336</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.207957</v>
+        <v>287.342117</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>318.970444</v>
+        <v>319.130131</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.334324</v>
+        <v>311.487651</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.698204</v>
+        <v>303.845171</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>296.062083</v>
+        <v>296.202692</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.425963</v>
+        <v>288.560212</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.317437</v>
+        <v>320.47727</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.64907</v>
+        <v>312.802529</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>304.980703</v>
+        <v>305.127788</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.312336</v>
+        <v>297.453047</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.643969</v>
+        <v>289.778307</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.664431</v>
+        <v>321.824409</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>313.963817</v>
+        <v>314.117407</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.263203</v>
+        <v>306.410405</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.562589</v>
+        <v>298.703403</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.861975</v>
+        <v>290.996401</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>323.011424</v>
+        <v>323.171548</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.278563</v>
+        <v>315.432285</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.545702</v>
+        <v>307.693022</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.812842</v>
+        <v>299.953759</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>292.079981</v>
+        <v>292.214496</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.04993</v>
+        <v>0.05036</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.15072</v>
+        <v>5.148453</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.920874</v>
+        <v>3.920208</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041218</v>
+        <v>0.041236</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.310737</v>
+        <v>8.307079999999999</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.407594</v>
+        <v>4.405562</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.120278</v>
+        <v>0.120331</v>
       </c>
     </row>
     <row r="4">
@@ -25947,13 +25947,13 @@
         <v/>
       </c>
       <c r="H4" s="9" t="n">
-        <v>5.483461</v>
+        <v>5.401133</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>5.176372</v>
+        <v>5.201985</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.091183</v>
+        <v>0.092573</v>
       </c>
     </row>
     <row r="5">
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>84.376745</v>
+        <v>84.33962200000001</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>15.055741</v>
+        <v>15.053141</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.011852</v>
+        <v>0.011857</v>
       </c>
     </row>
     <row r="8">
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1706.462397</v>
+        <v>1705.711603</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.397445</v>
+        <v>14.393063</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.2e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>38.852927</v>
+        <v>38.835833</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.665386</v>
+        <v>15.660056</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.716527</v>
+        <v>10.714611</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2547.860407</v>
+        <v>2548.279558</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.6925559903393</v>
+        <v>104.7386379957271</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2542.279703015659</v>
+        <v>2543.987238823125</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3632.928874082497</v>
+        <v>3635.20539321169</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3601.88725</v>
+        <v>3604.155568</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3331.489467</v>
+        <v>3333.615911</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3061.091684</v>
+        <v>3063.076255</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2790.693901</v>
+        <v>2792.536599</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2520.296118</v>
+        <v>2521.996943</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3617.408062</v>
+        <v>3619.68048</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3345.878024</v>
+        <v>3348.008383</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3074.347986</v>
+        <v>3076.336286</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2802.817948</v>
+        <v>2804.664188</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2531.28791</v>
+        <v>2532.992091</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3632.928874</v>
+        <v>3635.205393</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3360.266581</v>
+        <v>3362.400855</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3087.604289</v>
+        <v>3089.596316</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2814.941996</v>
+        <v>2816.791777</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2542.279703</v>
+        <v>2543.987239</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3648.449686</v>
+        <v>3650.730306</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3374.655139</v>
+        <v>3376.793326</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3100.860591</v>
+        <v>3102.856346</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2827.066043</v>
+        <v>2828.919367</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2553.271496</v>
+        <v>2554.982387</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3663.970499</v>
+        <v>3666.255219</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3389.043696</v>
+        <v>3391.185798</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3114.116893</v>
+        <v>3116.116377</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2839.190091</v>
+        <v>2841.046956</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2564.263288</v>
+        <v>2565.977535</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4975125911532087</v>
+        <v>0.4977315788136887</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2389.971001</v>
+        <v>2390.53783</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>295.8842405964722</v>
+        <v>296.014478501549</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1876.236198792732</v>
+        <v>1877.620359895535</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2325.988660683207</v>
+        <v>2327.656945956856</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2310.120912</v>
+        <v>2311.78554</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2195.043288</v>
+        <v>2196.635515</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2079.965664</v>
+        <v>2081.48549</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1964.88804</v>
+        <v>1966.335465</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1849.810415</v>
+        <v>1851.18544</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2321.718568</v>
+        <v>2323.386638</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2206.128808</v>
+        <v>2207.724354</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2090.539047</v>
+        <v>2092.062071</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1974.949286</v>
+        <v>1976.399788</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1859.359525</v>
+        <v>1860.737505</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2333.316225</v>
+        <v>2334.987735</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2217.214327</v>
+        <v>2218.813194</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2101.11243</v>
+        <v>2102.638653</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1985.010532</v>
+        <v>1986.464112</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1868.908635</v>
+        <v>1870.28957</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2344.913881</v>
+        <v>2346.588833</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2228.299847</v>
+        <v>2229.902034</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2111.685813</v>
+        <v>2113.215234</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1995.071779</v>
+        <v>1996.528435</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1878.457744</v>
+        <v>1879.841636</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2356.511537</v>
+        <v>2358.189931</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2239.385367</v>
+        <v>2240.990873</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2122.259196</v>
+        <v>2123.791816</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2005.133025</v>
+        <v>2006.592759</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1888.006854</v>
+        <v>1889.393701</v>
       </c>
     </row>
   </sheetData>
@@ -34730,7 +34730,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-26</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -34949,31 +34949,31 @@
         <v>0.1112</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.101353</v>
+        <v>0.1084</v>
       </c>
     </row>
     <row r="14">
@@ -35228,7 +35228,7 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>13200</v>
+        <v>11548</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>10702</v>
@@ -35270,34 +35270,34 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.14</v>
+        <v>0.095</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.115</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.213707</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
@@ -35357,7 +35357,7 @@
         <v>-0.013</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -38341,7 +38341,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>230068</v>
+        <v>238103</v>
       </c>
     </row>
     <row r="85">
@@ -38496,7 +38496,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>4249.791636</v>
+        <v>4656.957819</v>
       </c>
     </row>
     <row r="102">
@@ -38561,7 +38561,7 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>230068</v>
+        <v>238103</v>
       </c>
     </row>
     <row r="110">
@@ -38589,7 +38589,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="114">
@@ -38599,7 +38599,7 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="115">
@@ -38609,7 +38609,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="116">
@@ -38630,7 +38630,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>413.9721525448721</v>
+        <v>420.2821550913887</v>
       </c>
     </row>
     <row r="118">
@@ -38661,7 +38661,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>4992.370830783081</v>
+        <v>4042.740011534145</v>
       </c>
     </row>
     <row r="121">
@@ -38691,7 +38691,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>5651.267349617006</v>
+        <v>5969.101852352195</v>
       </c>
     </row>
     <row r="124">
@@ -38782,19 +38782,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>5660.311836</v>
+        <v>5638.968512</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>5466.623729</v>
+        <v>5299.376391</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>5272.935621</v>
+        <v>4959.78427</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>5079.247514</v>
+        <v>4620.192149</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>4885.559406</v>
+        <v>4280.600029</v>
       </c>
     </row>
     <row r="133">
@@ -38802,19 +38802,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>5686.967516</v>
+        <v>5665.558222</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>5492.429451</v>
+        <v>5324.475874</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>5297.891385</v>
+        <v>4983.393527</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>5103.353319</v>
+        <v>4642.31118</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>4908.815253</v>
+        <v>4301.228832</v>
       </c>
     </row>
     <row r="134">
@@ -38822,19 +38822,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>5713.623197</v>
+        <v>5692.147931</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>5518.235172</v>
+        <v>5349.575358</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>5322.847148</v>
+        <v>5007.002784</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>5127.459124</v>
+        <v>4664.43021</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>4932.0711</v>
+        <v>4321.857636</v>
       </c>
     </row>
     <row r="135">
@@ -38842,19 +38842,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>5740.278877</v>
+        <v>5718.737641</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>5544.040894</v>
+        <v>5374.674841</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>5347.802912</v>
+        <v>5030.61204</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>5151.564929</v>
+        <v>4686.54924</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>4955.326947</v>
+        <v>4342.48644</v>
       </c>
     </row>
     <row r="136">
@@ -38862,19 +38862,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>5766.934557</v>
+        <v>5745.327351</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>5569.846616</v>
+        <v>5399.774324</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>5372.758675</v>
+        <v>5054.221297</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>5175.670735</v>
+        <v>4708.66827</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>4978.582794</v>
+        <v>4363.115244</v>
       </c>
     </row>
   </sheetData>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.947588</v>
+        <v>1.946731</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.84989255641144</v>
+        <v>30.84329942127917</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>36.95163122665815</v>
+        <v>36.94503809152588</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.824009</v>
+        <v>1.824369</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.642694</v>
+        <v>36.636156</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.130013</v>
+        <v>35.123475</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.617332</v>
+        <v>33.610794</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.104651</v>
+        <v>32.098113</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.59197</v>
+        <v>30.585432</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.797163</v>
+        <v>36.790597</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.278105</v>
+        <v>35.271539</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.759047</v>
+        <v>33.752481</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.239989</v>
+        <v>32.233423</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.720931</v>
+        <v>30.714366</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>36.951631</v>
+        <v>36.945038</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.426197</v>
+        <v>35.419603</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.900762</v>
+        <v>33.894169</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.375327</v>
+        <v>32.368734</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.849893</v>
+        <v>30.843299</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.1061</v>
+        <v>37.099479</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.574288</v>
+        <v>35.567668</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.042477</v>
+        <v>34.035856</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.510665</v>
+        <v>32.504045</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>30.978854</v>
+        <v>30.972233</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.260568</v>
+        <v>37.25392</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.72238</v>
+        <v>35.715732</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.184192</v>
+        <v>34.177544</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.646004</v>
+        <v>32.639355</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.107815</v>
+        <v>31.101167</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18175</v>
+        <v>18183</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.183263971456725</v>
+        <v>1.183784802915963</v>
       </c>
     </row>
     <row r="92">
@@ -51122,7 +51122,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>8.562229</v>
+        <v>8.560313000000001</v>
       </c>
     </row>
     <row r="104">
@@ -51239,7 +51239,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>16.65150737904534</v>
+        <v>16.65883679082154</v>
       </c>
     </row>
     <row r="118">
@@ -51270,7 +51270,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1762.764775806316</v>
+        <v>1763.674697934074</v>
       </c>
     </row>
     <row r="121">
@@ -51300,7 +51300,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2144.662172895838</v>
+        <v>2145.720899181972</v>
       </c>
     </row>
     <row r="124">
@@ -51342,7 +51342,7 @@
         </is>
       </c>
       <c r="C127" s="18" t="n">
-        <v>0.831228</v>
+        <v>0.831134</v>
       </c>
     </row>
     <row r="128">
@@ -51483,19 +51483,19 @@
         <v>-0.01</v>
       </c>
       <c r="D141" s="23" t="n">
-        <v>2126.921031</v>
+        <v>2127.978196</v>
       </c>
       <c r="E141" s="23" t="n">
-        <v>2031.865906</v>
+        <v>2032.885692</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>1936.81078</v>
+        <v>1937.793187</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>1841.755654</v>
+        <v>1842.700683</v>
       </c>
       <c r="H141" s="23" t="n">
-        <v>1746.700528</v>
+        <v>1747.608179</v>
       </c>
     </row>
     <row r="142">
@@ -51503,19 +51503,19 @@
         <v>-0.005</v>
       </c>
       <c r="D142" s="23" t="n">
-        <v>2136.194861</v>
+        <v>2137.252984</v>
       </c>
       <c r="E142" s="23" t="n">
-        <v>2040.728494</v>
+        <v>2041.749238</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>1945.262127</v>
+        <v>1946.245493</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1849.79576</v>
+        <v>1850.741748</v>
       </c>
       <c r="H142" s="23" t="n">
-        <v>1754.329393</v>
+        <v>1755.238002</v>
       </c>
     </row>
     <row r="143">
@@ -51523,19 +51523,19 @@
         <v>0</v>
       </c>
       <c r="D143" s="23" t="n">
-        <v>2145.46869</v>
+        <v>2146.527771</v>
       </c>
       <c r="E143" s="23" t="n">
-        <v>2049.591082</v>
+        <v>2050.612785</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1953.713474</v>
+        <v>1954.697799</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>1857.835866</v>
+        <v>1858.782812</v>
       </c>
       <c r="H143" s="23" t="n">
-        <v>1761.958258</v>
+        <v>1762.867826</v>
       </c>
     </row>
     <row r="144">
@@ -51543,19 +51543,19 @@
         <v>0.005</v>
       </c>
       <c r="D144" s="23" t="n">
-        <v>2154.74252</v>
+        <v>2155.802559</v>
       </c>
       <c r="E144" s="23" t="n">
-        <v>2058.453671</v>
+        <v>2059.476332</v>
       </c>
       <c r="F144" s="23" t="n">
-        <v>1962.164822</v>
+        <v>1963.150104</v>
       </c>
       <c r="G144" s="23" t="n">
-        <v>1865.875973</v>
+        <v>1866.823877</v>
       </c>
       <c r="H144" s="23" t="n">
-        <v>1769.587124</v>
+        <v>1770.497649</v>
       </c>
     </row>
     <row r="145">
@@ -51563,19 +51563,19 @@
         <v>0.01</v>
       </c>
       <c r="D145" s="23" t="n">
-        <v>2164.016349</v>
+        <v>2165.077347</v>
       </c>
       <c r="E145" s="23" t="n">
-        <v>2067.316259</v>
+        <v>2068.339878</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1970.616169</v>
+        <v>1971.60241</v>
       </c>
       <c r="G145" s="23" t="n">
-        <v>1873.916079</v>
+        <v>1874.864941</v>
       </c>
       <c r="H145" s="23" t="n">
-        <v>1777.215989</v>
+        <v>1778.127473</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T02:00:09+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T10:26:30+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.76384520493933</v>
+        <v>38.76687401121073</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>53.03083191315557</v>
+        <v>53.03512433612789</v>
       </c>
     </row>
     <row r="118">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.88218</v>
+        <v>50.886262</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.256593</v>
+        <v>48.260464</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.631005</v>
+        <v>45.634666</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>43.005418</v>
+        <v>43.008868</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.379831</v>
+        <v>40.38307</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>51.108948</v>
+        <v>51.11303</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.471661</v>
+        <v>48.475532</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.834373</v>
+        <v>45.838034</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.197085</v>
+        <v>43.200535</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.559798</v>
+        <v>40.563037</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.335716</v>
+        <v>51.339798</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.686728</v>
+        <v>48.690599</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>46.03774</v>
+        <v>46.041401</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.388753</v>
+        <v>43.392203</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.739765</v>
+        <v>40.743004</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.562484</v>
+        <v>51.566566</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.901796</v>
+        <v>48.905667</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.241108</v>
+        <v>46.244769</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.58042</v>
+        <v>43.58387</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.919732</v>
+        <v>40.922971</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.789252</v>
+        <v>51.793333</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>49.116863</v>
+        <v>49.120735</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.444475</v>
+        <v>46.448136</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.772087</v>
+        <v>43.775537</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>41.099699</v>
+        <v>41.102939</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4884,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>208.365312</v>
+        <v>208.370262</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>200.858118751518</v>
+        <v>200.8789645817189</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>267.8108250020241</v>
+        <v>267.8386194422919</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.599447</v>
+        <v>3.599362</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>265.429507</v>
+        <v>265.457245</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>248.840163</v>
+        <v>248.866167</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>232.250819</v>
+        <v>232.275089</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>215.661475</v>
+        <v>215.684012</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>199.07213</v>
+        <v>199.092934</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>266.620166</v>
+        <v>266.647932</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>249.956406</v>
+        <v>249.982436</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>233.292645</v>
+        <v>233.316941</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>216.628885</v>
+        <v>216.651445</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>199.965125</v>
+        <v>199.985949</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>267.810825</v>
+        <v>267.838619</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>251.072648</v>
+        <v>251.098706</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>234.334472</v>
+        <v>234.358792</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>217.596295</v>
+        <v>217.618878</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>200.858119</v>
+        <v>200.878965</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>269.001484</v>
+        <v>269.029307</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>252.188891</v>
+        <v>252.214975</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>235.376298</v>
+        <v>235.400643</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>218.563706</v>
+        <v>218.586312</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>201.751113</v>
+        <v>201.77198</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>270.192143</v>
+        <v>270.219994</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>253.305134</v>
+        <v>253.331244</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>236.418125</v>
+        <v>236.442495</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>219.531116</v>
+        <v>219.553745</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>202.644107</v>
+        <v>202.664995</v>
       </c>
     </row>
   </sheetData>
@@ -9065,7 +9065,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -13153,7 +13153,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17299,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.7783065641057</v>
+        <v>289.8002322682146</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.4772699452854</v>
+        <v>320.5015184471065</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.782992</v>
+        <v>317.80724</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>310.172773</v>
+        <v>310.196441</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.562555</v>
+        <v>302.585642</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.952336</v>
+        <v>294.974842</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.342117</v>
+        <v>287.364043</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>319.130131</v>
+        <v>319.154379</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.487651</v>
+        <v>311.511319</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.845171</v>
+        <v>303.868259</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>296.202692</v>
+        <v>296.225198</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.560212</v>
+        <v>288.582138</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.47727</v>
+        <v>320.501518</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.802529</v>
+        <v>312.826197</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>305.127788</v>
+        <v>305.150875</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.453047</v>
+        <v>297.475554</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.778307</v>
+        <v>289.800232</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.824409</v>
+        <v>321.848657</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>314.117407</v>
+        <v>314.141075</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.410405</v>
+        <v>306.433492</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.703403</v>
+        <v>298.72591</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.996401</v>
+        <v>291.018327</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>323.171548</v>
+        <v>323.195796</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.432285</v>
+        <v>315.455953</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.693022</v>
+        <v>307.716109</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.953759</v>
+        <v>299.976265</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>292.214496</v>
+        <v>292.236422</v>
       </c>
     </row>
   </sheetData>
@@ -21492,7 +21492,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.05036</v>
+        <v>0.05045</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-28</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25700,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-28</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-28</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -26344,7 +26344,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2543.987238823125</v>
+        <v>2544.185151487221</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3635.20539321169</v>
+        <v>3635.484841641316</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3604.155568</v>
+        <v>3604.435016</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3333.615911</v>
+        <v>3333.874976</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3063.076255</v>
+        <v>3063.314936</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2792.536599</v>
+        <v>2792.754896</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2521.996943</v>
+        <v>2522.194855</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3619.68048</v>
+        <v>3619.959929</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3348.008383</v>
+        <v>3348.267448</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3076.336286</v>
+        <v>3076.574966</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2804.664188</v>
+        <v>2804.882485</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2532.992091</v>
+        <v>2533.190003</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3635.205393</v>
+        <v>3635.484842</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3362.400855</v>
+        <v>3362.659919</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3089.596316</v>
+        <v>3089.834997</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2816.791777</v>
+        <v>2817.010074</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2543.987239</v>
+        <v>2544.185151</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3650.730306</v>
+        <v>3651.009754</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3376.793326</v>
+        <v>3377.052391</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3102.856346</v>
+        <v>3103.095027</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2828.919367</v>
+        <v>2829.137663</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2554.982387</v>
+        <v>2555.180299</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3666.255219</v>
+        <v>3666.534667</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3391.185798</v>
+        <v>3391.444862</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3116.116377</v>
+        <v>3116.355057</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2841.046956</v>
+        <v>2841.265252</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2565.977535</v>
+        <v>2566.175447</v>
       </c>
     </row>
   </sheetData>
@@ -30537,7 +30537,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1877.620359895535</v>
+        <v>1877.792297071875</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2327.656945956856</v>
+        <v>2327.865765716856</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2311.78554</v>
+        <v>2311.99436</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2196.635515</v>
+        <v>2196.835114</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2081.48549</v>
+        <v>2081.675868</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1966.335465</v>
+        <v>1966.516623</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1851.18544</v>
+        <v>1851.357377</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2323.386638</v>
+        <v>2323.595457</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2207.724354</v>
+        <v>2207.923954</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2092.062071</v>
+        <v>2092.25245</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1976.399788</v>
+        <v>1976.580946</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1860.737505</v>
+        <v>1860.909442</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2334.987735</v>
+        <v>2335.196555</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2218.813194</v>
+        <v>2219.012793</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2102.638653</v>
+        <v>2102.829031</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1986.464112</v>
+        <v>1986.64527</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1870.28957</v>
+        <v>1870.461508</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2346.588833</v>
+        <v>2346.797653</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2229.902034</v>
+        <v>2230.101633</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2113.215234</v>
+        <v>2113.405613</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1996.528435</v>
+        <v>1996.709593</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1879.841636</v>
+        <v>1880.013573</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2358.189931</v>
+        <v>2358.398751</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2240.990873</v>
+        <v>2241.190473</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2123.791816</v>
+        <v>2123.982195</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2006.592759</v>
+        <v>2006.773916</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1889.393701</v>
+        <v>1889.565638</v>
       </c>
     </row>
   </sheetData>
@@ -38906,7 +38906,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -43092,7 +43092,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -47322,7 +47322,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-28 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -47457,31 +47457,31 @@
         <v>0.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12">
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>1919.124899</v>
+        <v>946.284416</v>
       </c>
     </row>
     <row r="102">
@@ -51270,7 +51270,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1763.674697934074</v>
+        <v>1180.313692476305</v>
       </c>
     </row>
     <row r="121">
@@ -51300,7 +51300,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2145.720899181972</v>
+        <v>1367.890055653173</v>
       </c>
     </row>
     <row r="124">
@@ -51342,7 +51342,7 @@
         </is>
       </c>
       <c r="C127" s="18" t="n">
-        <v>0.831134</v>
+        <v>1.269475</v>
       </c>
     </row>
     <row r="128">
@@ -51362,7 +51362,7 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="130">
@@ -51402,7 +51402,7 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="134">
@@ -51483,19 +51483,19 @@
         <v>-0.01</v>
       </c>
       <c r="D141" s="23" t="n">
-        <v>2127.978196</v>
+        <v>1356.818259</v>
       </c>
       <c r="E141" s="23" t="n">
-        <v>2032.885692</v>
+        <v>1309.926282</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>1937.793187</v>
+        <v>1263.034306</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>1842.700683</v>
+        <v>1216.142329</v>
       </c>
       <c r="H141" s="23" t="n">
-        <v>1747.608179</v>
+        <v>1169.250353</v>
       </c>
     </row>
     <row r="142">
@@ -51503,19 +51503,19 @@
         <v>-0.005</v>
       </c>
       <c r="D142" s="23" t="n">
-        <v>2137.252984</v>
+        <v>1362.757593</v>
       </c>
       <c r="E142" s="23" t="n">
-        <v>2041.749238</v>
+        <v>1315.662842</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>1946.245493</v>
+        <v>1268.56809</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1850.741748</v>
+        <v>1221.473338</v>
       </c>
       <c r="H142" s="23" t="n">
-        <v>1755.238002</v>
+        <v>1174.378587</v>
       </c>
     </row>
     <row r="143">
@@ -51523,19 +51523,19 @@
         <v>0</v>
       </c>
       <c r="D143" s="23" t="n">
-        <v>2146.527771</v>
+        <v>1368.696928</v>
       </c>
       <c r="E143" s="23" t="n">
-        <v>2050.612785</v>
+        <v>1321.399401</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1954.697799</v>
+        <v>1274.101874</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>1858.782812</v>
+        <v>1226.804347</v>
       </c>
       <c r="H143" s="23" t="n">
-        <v>1762.867826</v>
+        <v>1179.50682</v>
       </c>
     </row>
     <row r="144">
@@ -51543,19 +51543,19 @@
         <v>0.005</v>
       </c>
       <c r="D144" s="23" t="n">
-        <v>2155.802559</v>
+        <v>1374.636263</v>
       </c>
       <c r="E144" s="23" t="n">
-        <v>2059.476332</v>
+        <v>1327.13596</v>
       </c>
       <c r="F144" s="23" t="n">
-        <v>1963.150104</v>
+        <v>1279.635658</v>
       </c>
       <c r="G144" s="23" t="n">
-        <v>1866.823877</v>
+        <v>1232.135356</v>
       </c>
       <c r="H144" s="23" t="n">
-        <v>1770.497649</v>
+        <v>1184.635054</v>
       </c>
     </row>
     <row r="145">
@@ -51563,19 +51563,19 @@
         <v>0.01</v>
       </c>
       <c r="D145" s="23" t="n">
-        <v>2165.077347</v>
+        <v>1380.575597</v>
       </c>
       <c r="E145" s="23" t="n">
-        <v>2068.339878</v>
+        <v>1332.87252</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1971.60241</v>
+        <v>1285.169442</v>
       </c>
       <c r="G145" s="23" t="n">
-        <v>1874.864941</v>
+        <v>1237.466365</v>
       </c>
       <c r="H145" s="23" t="n">
-        <v>1778.127473</v>
+        <v>1189.763287</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T10:26:30+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T13:53:09+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4569708560601814</v>
+        <v>0.4548849196881309</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.31252</v>
+        <v>39.13307</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.845401</v>
+        <v>0.8492769999999999</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005921282346156363</v>
+        <v>0.005894253449124466</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.76687401121073</v>
+        <v>38.62824495584726</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>53.03512433612789</v>
+        <v>52.82855097285852</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.415948</v>
+        <v>12.461765</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.886262</v>
+        <v>50.690087</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.260464</v>
+        <v>48.076503</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.634666</v>
+        <v>45.462919</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>43.008868</v>
+        <v>42.849336</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.38307</v>
+        <v>40.235752</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>51.11303</v>
+        <v>50.916</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.475532</v>
+        <v>48.29077</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.838034</v>
+        <v>45.665539</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.200535</v>
+        <v>43.040309</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.563037</v>
+        <v>40.415078</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.339798</v>
+        <v>51.141914</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.690599</v>
+        <v>48.505036</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>46.041401</v>
+        <v>45.868159</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.392203</v>
+        <v>43.231282</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.743004</v>
+        <v>40.594404</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.566566</v>
+        <v>51.367827</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.905667</v>
+        <v>48.719303</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.244769</v>
+        <v>46.070779</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.58387</v>
+        <v>43.422255</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.922971</v>
+        <v>40.77373</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.793333</v>
+        <v>51.59374</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>49.120735</v>
+        <v>48.933569</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.448136</v>
+        <v>46.273398</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.775537</v>
+        <v>43.613228</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>41.102939</v>
+        <v>40.953057</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2994399219833106</v>
+        <v>0.2980730675849926</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>208.370262</v>
+        <v>207.845503</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>200.8789645817189</v>
+        <v>200.3616359585882</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>267.8386194422919</v>
+        <v>267.1488479447842</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.599362</v>
+        <v>3.608449</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>265.457245</v>
+        <v>264.773471</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>248.866167</v>
+        <v>248.225129</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>232.275089</v>
+        <v>231.676787</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>215.684012</v>
+        <v>215.128445</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>199.092934</v>
+        <v>198.580103</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>266.647932</v>
+        <v>265.961159</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>249.982436</v>
+        <v>249.338587</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>233.316941</v>
+        <v>232.716014</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>216.651445</v>
+        <v>216.093442</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>199.985949</v>
+        <v>199.47087</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>267.838619</v>
+        <v>267.148848</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>251.098706</v>
+        <v>250.452045</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>234.358792</v>
+        <v>233.755242</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>217.618878</v>
+        <v>217.058439</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>200.878965</v>
+        <v>200.361636</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>269.029307</v>
+        <v>268.336537</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>252.214975</v>
+        <v>251.565503</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>235.400643</v>
+        <v>234.794469</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>218.586312</v>
+        <v>218.023436</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>201.77198</v>
+        <v>201.252402</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>270.219994</v>
+        <v>269.524225</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>253.331244</v>
+        <v>252.678961</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>236.442495</v>
+        <v>235.833697</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>219.553745</v>
+        <v>218.988433</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>202.664995</v>
+        <v>202.143169</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.680095381571204</v>
+        <v>1.672426244648232</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.551704</v>
+        <v>149.86448</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.845401</v>
+        <v>0.8492769999999999</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.439976</v>
+        <v>15.493601</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.8002322682146</v>
+        <v>289.4932900746586</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.5015184471065</v>
+        <v>320.0451807980241</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.80724</v>
+        <v>317.353924</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>310.196441</v>
+        <v>309.780179</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.585642</v>
+        <v>302.206434</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.974842</v>
+        <v>294.632689</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.364043</v>
+        <v>287.058944</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>319.154379</v>
+        <v>318.699552</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.511319</v>
+        <v>311.093694</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.868259</v>
+        <v>303.487835</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>296.225198</v>
+        <v>295.881976</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.582138</v>
+        <v>288.276117</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.501518</v>
+        <v>320.045181</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.826197</v>
+        <v>312.407208</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>305.150875</v>
+        <v>304.769235</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.475554</v>
+        <v>297.131263</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.800232</v>
+        <v>289.49329</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.848657</v>
+        <v>321.390809</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>314.141075</v>
+        <v>313.720723</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.433492</v>
+        <v>306.050636</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.72591</v>
+        <v>298.38055</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>291.018327</v>
+        <v>290.710463</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>323.195796</v>
+        <v>322.736437</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.455953</v>
+        <v>315.034237</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.716109</v>
+        <v>307.332037</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.976265</v>
+        <v>299.629837</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>292.236422</v>
+        <v>291.927636</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.148453</v>
+        <v>5.172062</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.920208</v>
+        <v>3.927146</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041236</v>
+        <v>0.041047</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.307079999999999</v>
+        <v>8.345173000000001</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.405562</v>
+        <v>4.426733</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.120331</v>
+        <v>0.119782</v>
       </c>
     </row>
     <row r="4">
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>84.33962200000001</v>
+        <v>84.726373</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>15.053141</v>
+        <v>15.080226</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.011857</v>
+        <v>0.011803</v>
       </c>
     </row>
     <row r="8">
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1705.711603</v>
+        <v>1713.533374</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.393063</v>
+        <v>14.438723</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.2e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>38.835833</v>
+        <v>39.01392</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.660056</v>
+        <v>15.71559</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.714611</v>
+        <v>10.734573</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2548.279558</v>
+        <v>2543.930871</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.7386379957271</v>
+        <v>104.260537189829</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2544.185151487221</v>
+        <v>2536.276267773817</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3635.484841641316</v>
+        <v>3625.713634631339</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3604.435016</v>
+        <v>3594.748895</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3333.874976</v>
+        <v>3324.65057</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3063.314936</v>
+        <v>3054.552246</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2792.754896</v>
+        <v>2784.453922</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2522.194855</v>
+        <v>2514.355597</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3619.959929</v>
+        <v>3610.231265</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3348.267448</v>
+        <v>3339.002432</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3076.574966</v>
+        <v>3067.773599</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2804.882485</v>
+        <v>2796.544766</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2533.190003</v>
+        <v>2525.315932</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3635.484842</v>
+        <v>3625.713635</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3362.659919</v>
+        <v>3353.354293</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3089.834997</v>
+        <v>3080.994951</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2817.010074</v>
+        <v>2808.635609</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2544.185151</v>
+        <v>2536.276268</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3651.009754</v>
+        <v>3641.196005</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3377.052391</v>
+        <v>3367.706154</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3103.095027</v>
+        <v>3094.216304</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2829.137663</v>
+        <v>2820.726453</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2555.180299</v>
+        <v>2547.236603</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3666.534667</v>
+        <v>3656.678375</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3391.444862</v>
+        <v>3382.058016</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3116.355057</v>
+        <v>3107.437656</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2841.265252</v>
+        <v>2832.817297</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2566.175447</v>
+        <v>2558.196938</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4977315788136887</v>
+        <v>0.4954595818362078</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2390.53783</v>
+        <v>2384.656982</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>296.014478501549</v>
+        <v>294.6632602363767</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1877.792297071875</v>
+        <v>1871.951858119835</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2327.865765716856</v>
+        <v>2320.905360640848</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2311.99436</v>
+        <v>2305.071903</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2196.835114</v>
+        <v>2190.20686</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2081.675868</v>
+        <v>2075.341817</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1966.516623</v>
+        <v>1960.476774</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1851.357377</v>
+        <v>1845.611731</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2323.595457</v>
+        <v>2316.637295</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2207.923954</v>
+        <v>2201.261254</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2092.25245</v>
+        <v>2085.885213</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1976.580946</v>
+        <v>1970.509172</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1860.909442</v>
+        <v>1855.133131</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2335.196555</v>
+        <v>2328.202687</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2219.012793</v>
+        <v>2212.315648</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2102.829031</v>
+        <v>2096.428609</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1986.64527</v>
+        <v>1980.54157</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1870.461508</v>
+        <v>1864.654532</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2346.797653</v>
+        <v>2339.768079</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2230.101633</v>
+        <v>2223.370043</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2113.405613</v>
+        <v>2106.972006</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1996.709593</v>
+        <v>1990.573969</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1880.013573</v>
+        <v>1874.175932</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2358.398751</v>
+        <v>2351.333472</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2241.190473</v>
+        <v>2234.424437</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2123.982195</v>
+        <v>2117.515402</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2006.773916</v>
+        <v>2000.606367</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1889.565638</v>
+        <v>1883.697333</v>
       </c>
     </row>
   </sheetData>
@@ -35273,31 +35273,31 @@
         <v>0.095</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.115</v>
+        <v>0.14</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23">
@@ -35357,7 +35357,7 @@
         <v>-0.013</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -38496,7 +38496,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>4656.957819</v>
+        <v>4514.086912</v>
       </c>
     </row>
     <row r="102">
@@ -38661,7 +38661,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>4042.740011534145</v>
+        <v>3916.622517226187</v>
       </c>
     </row>
     <row r="121">
@@ -38691,7 +38691,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>5969.101852352195</v>
+        <v>5779.925610890258</v>
       </c>
     </row>
     <row r="124">
@@ -38782,19 +38782,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>5638.968512</v>
+        <v>5461.856497</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>5299.376391</v>
+        <v>5132.68273</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>4959.78427</v>
+        <v>4803.508963</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>4620.192149</v>
+        <v>4474.335196</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>4280.600029</v>
+        <v>4145.161429</v>
       </c>
     </row>
     <row r="133">
@@ -38802,19 +38802,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>5665.558222</v>
+        <v>5487.668989</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>5324.475874</v>
+        <v>5157.050714</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>4983.393527</v>
+        <v>4826.432439</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>4642.31118</v>
+        <v>4495.814165</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>4301.228832</v>
+        <v>4165.19589</v>
       </c>
     </row>
     <row r="134">
@@ -38822,19 +38822,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>5692.147931</v>
+        <v>5513.481481</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>5349.575358</v>
+        <v>5181.418698</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>5007.002784</v>
+        <v>4849.355916</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>4664.43021</v>
+        <v>4517.293133</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>4321.857636</v>
+        <v>4185.230351</v>
       </c>
     </row>
     <row r="135">
@@ -38842,19 +38842,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>5718.737641</v>
+        <v>5539.293973</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>5374.674841</v>
+        <v>5205.786683</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>5030.61204</v>
+        <v>4872.279392</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>4686.54924</v>
+        <v>4538.772102</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>4342.48644</v>
+        <v>4205.264811</v>
       </c>
     </row>
     <row r="136">
@@ -38862,19 +38862,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>5745.327351</v>
+        <v>5565.106465</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>5399.774324</v>
+        <v>5230.154667</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>5054.221297</v>
+        <v>4895.202869</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>4708.66827</v>
+        <v>4560.25107</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>4363.115244</v>
+        <v>4225.299272</v>
       </c>
     </row>
   </sheetData>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.946731</v>
+        <v>1.955658</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.84329942127917</v>
+        <v>30.91198663934143</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>36.94503809152588</v>
+        <v>37.01372530958814</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.824369</v>
+        <v>1.820629</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.636156</v>
+        <v>36.704269</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.123475</v>
+        <v>35.191588</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.610794</v>
+        <v>33.678907</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.098113</v>
+        <v>32.166226</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.585432</v>
+        <v>30.653545</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.790597</v>
+        <v>36.858997</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.271539</v>
+        <v>35.339939</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.752481</v>
+        <v>33.820881</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.233423</v>
+        <v>32.301824</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.714366</v>
+        <v>30.782766</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>36.945038</v>
+        <v>37.013725</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.419603</v>
+        <v>35.488291</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.894169</v>
+        <v>33.962856</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.368734</v>
+        <v>32.437421</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.843299</v>
+        <v>30.911987</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.099479</v>
+        <v>37.168453</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.567668</v>
+        <v>35.636642</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.035856</v>
+        <v>34.10483</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.504045</v>
+        <v>32.573019</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>30.972233</v>
+        <v>31.041208</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.25392</v>
+        <v>37.323181</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.715732</v>
+        <v>35.784993</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.177544</v>
+        <v>34.246805</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.639355</v>
+        <v>32.708617</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.101167</v>
+        <v>31.170429</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.183784802915963</v>
+        <v>1.178381176526367</v>
       </c>
     </row>
     <row r="92">
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>946.284416</v>
+        <v>1138.996164</v>
       </c>
     </row>
     <row r="102">
@@ -51122,7 +51122,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>8.560313000000001</v>
+        <v>8.580268999999999</v>
       </c>
     </row>
     <row r="104">
@@ -51239,7 +51239,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>16.65883679082154</v>
+        <v>16.5827941436435</v>
       </c>
     </row>
     <row r="118">
@@ -51270,7 +51270,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1180.313692476305</v>
+        <v>1293.368451285954</v>
       </c>
     </row>
     <row r="121">
@@ -51300,7 +51300,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>1367.890055653173</v>
+        <v>1519.431380258833</v>
       </c>
     </row>
     <row r="124">
@@ -51342,7 +51342,7 @@
         </is>
       </c>
       <c r="C127" s="18" t="n">
-        <v>1.269475</v>
+        <v>1.151266</v>
       </c>
     </row>
     <row r="128">
@@ -51483,19 +51483,19 @@
         <v>-0.01</v>
       </c>
       <c r="D141" s="23" t="n">
-        <v>1356.818259</v>
+        <v>1507.054332</v>
       </c>
       <c r="E141" s="23" t="n">
-        <v>1309.926282</v>
+        <v>1450.625146</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>1263.034306</v>
+        <v>1394.195961</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>1216.142329</v>
+        <v>1337.766775</v>
       </c>
       <c r="H141" s="23" t="n">
-        <v>1169.250353</v>
+        <v>1281.337589</v>
       </c>
     </row>
     <row r="142">
@@ -51503,19 +51503,19 @@
         <v>-0.005</v>
       </c>
       <c r="D142" s="23" t="n">
-        <v>1362.757593</v>
+        <v>1513.644451</v>
       </c>
       <c r="E142" s="23" t="n">
-        <v>1315.662842</v>
+        <v>1456.971194</v>
       </c>
       <c r="F142" s="23" t="n">
-        <v>1268.56809</v>
+        <v>1400.297938</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1221.473338</v>
+        <v>1343.624682</v>
       </c>
       <c r="H142" s="23" t="n">
-        <v>1174.378587</v>
+        <v>1286.951426</v>
       </c>
     </row>
     <row r="143">
@@ -51523,19 +51523,19 @@
         <v>0</v>
       </c>
       <c r="D143" s="23" t="n">
-        <v>1368.696928</v>
+        <v>1520.234569</v>
       </c>
       <c r="E143" s="23" t="n">
-        <v>1321.399401</v>
+        <v>1463.317243</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1274.101874</v>
+        <v>1406.399916</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>1226.804347</v>
+        <v>1349.482589</v>
       </c>
       <c r="H143" s="23" t="n">
-        <v>1179.50682</v>
+        <v>1292.565262</v>
       </c>
     </row>
     <row r="144">
@@ -51543,19 +51543,19 @@
         <v>0.005</v>
       </c>
       <c r="D144" s="23" t="n">
-        <v>1374.636263</v>
+        <v>1526.824688</v>
       </c>
       <c r="E144" s="23" t="n">
-        <v>1327.13596</v>
+        <v>1469.663291</v>
       </c>
       <c r="F144" s="23" t="n">
-        <v>1279.635658</v>
+        <v>1412.501893</v>
       </c>
       <c r="G144" s="23" t="n">
-        <v>1232.135356</v>
+        <v>1355.340496</v>
       </c>
       <c r="H144" s="23" t="n">
-        <v>1184.635054</v>
+        <v>1298.179098</v>
       </c>
     </row>
     <row r="145">
@@ -51563,19 +51563,19 @@
         <v>0.01</v>
       </c>
       <c r="D145" s="23" t="n">
-        <v>1380.575597</v>
+        <v>1533.414807</v>
       </c>
       <c r="E145" s="23" t="n">
-        <v>1332.87252</v>
+        <v>1476.009339</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>1285.169442</v>
+        <v>1418.603871</v>
       </c>
       <c r="G145" s="23" t="n">
-        <v>1237.466365</v>
+        <v>1361.198403</v>
       </c>
       <c r="H145" s="23" t="n">
-        <v>1189.763287</v>
+        <v>1303.792935</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T13:53:09+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T01:56:00+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4548849196881309</v>
+        <v>0.4555132137760979</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.13307</v>
+        <v>39.187121</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.8492769999999999</v>
+        <v>0.848106</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005894253449124466</v>
+        <v>0.005902394683170218</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.62824495584726</v>
+        <v>38.65791260589593</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>52.82855097285852</v>
+        <v>52.87364411030559</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.461765</v>
+        <v>12.447929</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.690087</v>
+        <v>50.732888</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.076503</v>
+        <v>48.116465</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.462919</v>
+        <v>45.500042</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>42.849336</v>
+        <v>42.883619</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.235752</v>
+        <v>40.267197</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>50.916</v>
+        <v>50.959059</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.29077</v>
+        <v>48.330973</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.665539</v>
+        <v>45.702887</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.040309</v>
+        <v>43.074802</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.415078</v>
+        <v>40.446716</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.141914</v>
+        <v>51.185229</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.505036</v>
+        <v>48.545481</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>45.868159</v>
+        <v>45.905732</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.231282</v>
+        <v>43.265984</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.594404</v>
+        <v>40.626235</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.367827</v>
+        <v>51.4114</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.719303</v>
+        <v>48.759989</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.070779</v>
+        <v>46.108577</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.422255</v>
+        <v>43.457166</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.77373</v>
+        <v>40.805755</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.59374</v>
+        <v>51.637571</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>48.933569</v>
+        <v>48.974497</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.273398</v>
+        <v>46.311422</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.613228</v>
+        <v>43.648348</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>40.953057</v>
+        <v>40.985274</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2980730675849926</v>
+        <v>0.2984847707170161</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>207.845503</v>
+        <v>207.865779</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>200.3616359585882</v>
+        <v>200.3204853322435</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>267.1488479447842</v>
+        <v>267.0939804429914</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.608449</v>
+        <v>3.608098</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>264.773471</v>
+        <v>264.718372</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>248.225129</v>
+        <v>248.173473</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>231.676787</v>
+        <v>231.628575</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>215.128445</v>
+        <v>215.083677</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>198.580103</v>
+        <v>198.538779</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>265.961159</v>
+        <v>265.906176</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>249.338587</v>
+        <v>249.28704</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>232.716014</v>
+        <v>232.667904</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>216.093442</v>
+        <v>216.048768</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>199.47087</v>
+        <v>199.429632</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>267.148848</v>
+        <v>267.09398</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>250.452045</v>
+        <v>250.400607</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>233.755242</v>
+        <v>233.707233</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>217.058439</v>
+        <v>217.013859</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>200.361636</v>
+        <v>200.320485</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>268.336537</v>
+        <v>268.281785</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>251.565503</v>
+        <v>251.514173</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>234.794469</v>
+        <v>234.746562</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>218.023436</v>
+        <v>217.97895</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>201.252402</v>
+        <v>201.211339</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>269.524225</v>
+        <v>269.469589</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>252.678961</v>
+        <v>252.62774</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>235.833697</v>
+        <v>235.785891</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>218.988433</v>
+        <v>218.944041</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>202.143169</v>
+        <v>202.102192</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.672426244648232</v>
+        <v>1.674736225649127</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>149.86448</v>
+        <v>150.071475</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.8492769999999999</v>
+        <v>0.848106</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.493601</v>
+        <v>15.477397</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.4932900746586</v>
+        <v>289.4980721222381</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.0451807980241</v>
+        <v>320.0856909918504</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.353924</v>
+        <v>317.393524</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>309.780179</v>
+        <v>309.810936</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.206434</v>
+        <v>302.228348</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.632689</v>
+        <v>294.645759</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.058944</v>
+        <v>287.063171</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>318.699552</v>
+        <v>318.739608</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.093694</v>
+        <v>311.124861</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.487835</v>
+        <v>303.510115</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>295.881976</v>
+        <v>295.895368</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.276117</v>
+        <v>288.280621</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.045181</v>
+        <v>320.085691</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.407208</v>
+        <v>312.438786</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>304.769235</v>
+        <v>304.791882</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.131263</v>
+        <v>297.144977</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.49329</v>
+        <v>289.498072</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.390809</v>
+        <v>321.431774</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>313.720723</v>
+        <v>313.752711</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.050636</v>
+        <v>306.073649</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.38055</v>
+        <v>298.394586</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.710463</v>
+        <v>290.715523</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>322.736437</v>
+        <v>322.777858</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.034237</v>
+        <v>315.066637</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.332037</v>
+        <v>307.355416</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.629837</v>
+        <v>299.644194</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>291.927636</v>
+        <v>291.932973</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.05045</v>
+        <v>0.05009</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.172062</v>
+        <v>5.164928</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.927146</v>
+        <v>3.92505</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041047</v>
+        <v>0.041104</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.345173000000001</v>
+        <v>8.333663</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.426733</v>
+        <v>4.420335</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.119782</v>
+        <v>0.119947</v>
       </c>
     </row>
     <row r="4">
@@ -26048,11 +26048,11 @@
         </is>
       </c>
       <c r="C7" s="6">
-        <f>'BRPT'!$C$137</f>
+        <f>'BRPT'!$C$125</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>'BRPT'!$C$135</f>
+        <f>'BRPT'!$C$123</f>
         <v/>
       </c>
       <c r="E7" s="7">
@@ -26060,21 +26060,21 @@
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>'BRPT'!$C$136</f>
+        <f>'BRPT'!$C$124</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>'BRPT'!$C$116</f>
+        <f>'BRPT'!$C$104</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>84.726373</v>
+        <v>23.138996</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>15.080226</v>
+        <v>7.889215</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.011803</v>
+        <v>0.004322</v>
       </c>
     </row>
     <row r="8">
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1713.533374</v>
+        <v>1711.16988</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.438723</v>
+        <v>14.424926</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.2e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>39.01392</v>
+        <v>38.960107</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.71559</v>
+        <v>15.698809</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.734573</v>
+        <v>10.728541</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2543.930871</v>
+        <v>2545.240717</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.260537189829</v>
+        <v>104.4045434566658</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2536.276267773817</v>
+        <v>2537.868562546187</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3625.713634631339</v>
+        <v>3627.541116021459</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3594.748895</v>
+        <v>3596.550748</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3324.65057</v>
+        <v>3326.394791</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3054.552246</v>
+        <v>3056.238834</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2784.453922</v>
+        <v>2786.082877</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2514.355597</v>
+        <v>2515.92692</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3610.231265</v>
+        <v>3612.045932</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3339.002432</v>
+        <v>3340.758884</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3067.773599</v>
+        <v>3069.471837</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2796.544766</v>
+        <v>2798.184789</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2525.315932</v>
+        <v>2526.897741</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3625.713635</v>
+        <v>3627.541116</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3353.354293</v>
+        <v>3355.122978</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3080.994951</v>
+        <v>3082.704839</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2808.635609</v>
+        <v>2810.286701</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2536.276268</v>
+        <v>2537.868563</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3641.196005</v>
+        <v>3643.0363</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3367.706154</v>
+        <v>3369.487071</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3094.216304</v>
+        <v>3095.937842</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2820.726453</v>
+        <v>2822.388613</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2547.236603</v>
+        <v>2548.839384</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3656.678375</v>
+        <v>3658.531484</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3382.058016</v>
+        <v>3383.851164</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3107.437656</v>
+        <v>3109.170844</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2832.817297</v>
+        <v>2834.490525</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2558.196938</v>
+        <v>2559.810205</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4954595818362078</v>
+        <v>0.4961439182752081</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2384.656982</v>
+        <v>2386.428322</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>294.6632602363767</v>
+        <v>295.0702536897418</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1871.951858119835</v>
+        <v>1873.024682883861</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2320.905360640848</v>
+        <v>2322.168225238017</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2305.071903</v>
+        <v>2306.323337</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2190.20686</v>
+        <v>2191.406504</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2075.341817</v>
+        <v>2076.48967</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1960.476774</v>
+        <v>1961.572837</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1845.611731</v>
+        <v>1846.656003</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2316.637295</v>
+        <v>2317.899484</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2201.261254</v>
+        <v>2202.471273</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2085.885213</v>
+        <v>2087.043062</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1970.509172</v>
+        <v>1971.614851</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1855.133131</v>
+        <v>1856.18664</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2328.202687</v>
+        <v>2329.475631</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2212.315648</v>
+        <v>2213.536043</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2096.428609</v>
+        <v>2097.596454</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1980.54157</v>
+        <v>1981.656866</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1864.654532</v>
+        <v>1865.717277</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2339.768079</v>
+        <v>2341.051778</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2223.370043</v>
+        <v>2224.600812</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2106.972006</v>
+        <v>2108.149846</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1990.573969</v>
+        <v>1991.69888</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1874.175932</v>
+        <v>1875.247914</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2351.333472</v>
+        <v>2352.627925</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2234.424437</v>
+        <v>2235.665581</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2117.515402</v>
+        <v>2118.703238</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2000.606367</v>
+        <v>2001.740894</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1883.697333</v>
+        <v>1884.778551</v>
       </c>
     </row>
   </sheetData>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.955658</v>
+        <v>1.952961</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.91198663934143</v>
+        <v>30.89123151369081</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>37.01372530958814</v>
+        <v>36.99297018393752</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.820629</v>
+        <v>1.821757</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.704269</v>
+        <v>36.683688</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.191588</v>
+        <v>35.171006</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.678907</v>
+        <v>33.658325</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.166226</v>
+        <v>32.145644</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.653545</v>
+        <v>30.632963</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.858997</v>
+        <v>36.838329</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.339939</v>
+        <v>35.319271</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.820881</v>
+        <v>33.800213</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.301824</v>
+        <v>32.281155</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.782766</v>
+        <v>30.762097</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>37.013725</v>
+        <v>36.99297</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.488291</v>
+        <v>35.467536</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.962856</v>
+        <v>33.942101</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.437421</v>
+        <v>32.416666</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.911987</v>
+        <v>30.891232</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.168453</v>
+        <v>37.147611</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.636642</v>
+        <v>35.6158</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.10483</v>
+        <v>34.083989</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.573019</v>
+        <v>32.552177</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>31.041208</v>
+        <v>31.020366</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.323181</v>
+        <v>37.302253</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.784993</v>
+        <v>35.764065</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.246805</v>
+        <v>34.225876</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.708617</v>
+        <v>32.687688</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.170429</v>
+        <v>31.1495</v>
       </c>
     </row>
   </sheetData>
@@ -47304,7 +47304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -47322,7 +47322,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -47454,7 +47454,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3</v>
+        <v>0.490285</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0.1</v>
@@ -47496,34 +47496,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.191901</v>
+        <v>0.213614</v>
       </c>
     </row>
     <row r="13">
@@ -47538,34 +47538,34 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.111429</v>
+        <v>0.069364</v>
       </c>
     </row>
     <row r="14">
@@ -47580,34 +47580,34 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.043116</v>
+        <v>0.039247</v>
       </c>
     </row>
     <row r="15">
@@ -47904,34 +47904,34 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -48479,10 +48479,10 @@
         <v>300.843</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>320.228</v>
+        <v>320.399</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>390.532</v>
+        <v>379.275</v>
       </c>
       <c r="H36" s="14">
         <f>(G56*$C$18)</f>
@@ -48607,10 +48607,10 @@
         <v>70.84099999999999</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>85.63799999999998</v>
+        <v>85.80899999999997</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>2046.023</v>
+        <v>2034.766</v>
       </c>
       <c r="H38" s="14">
         <f>H21</f>
@@ -49250,7 +49250,7 @@
         <v>521.285</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>913.247</v>
+        <v>915.3</v>
       </c>
       <c r="H48" s="14">
         <f>(H29*H15)</f>
@@ -49374,7 +49374,7 @@
         <v>-546.6809086877295</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>-1003.08802574068</v>
+        <v>-1005.14102574068</v>
       </c>
       <c r="H50" s="14">
         <f>((((H33*(1-H17))+H34)-H48)-H49)</f>
@@ -50814,7 +50814,7 @@
         <v>0.2183854595422278</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.119681228181775</v>
+        <v>0.1199502743012336</v>
       </c>
       <c r="H73" s="17">
         <f>IF(H29=0,0,H48/H29)</f>
@@ -50871,7 +50871,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>1405</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="77">
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.178381176526367</v>
+        <v>1.342439132506286</v>
       </c>
     </row>
     <row r="92">
@@ -51105,477 +51105,381 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>1138.996164</v>
+        <v>1139.042678</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>P/E</t>
+          <t>TARGET</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Target multiple (peer median (own history unavailable))</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="n">
-        <v>8.580268999999999</v>
+          <t>Weight: Sum of the parts</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Metric (LTM, or next-12m DPS for yield)</t>
-        </is>
-      </c>
-      <c r="C104" s="13" t="n">
-        <v>489.807</v>
+          <t>Value today (weighted)</t>
+        </is>
+      </c>
+      <c r="C104" s="23">
+        <f>$C$100*$C$103</f>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — P/E</t>
-        </is>
-      </c>
-      <c r="C105" s="23">
-        <f>MAX(0,$C$103*$C$104/$C$77*$C$85*$C$78)</f>
+          <t>DPS expected in next 12 months (IDR)</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="n">
+        <v>5.337310312020393</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Base-case 12-month value</t>
+        </is>
+      </c>
+      <c r="C106" s="23">
+        <f>MAX(0,$C$104*(1+$C$94)-$C$105)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>P/BV</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Bear probability</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Target multiple (own five-year average)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n">
-        <v>4.737987</v>
+          <t>Bear 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n">
+        <v>1142.316793508954</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Metric (LTM, or next-12m DPS for yield)</t>
-        </is>
-      </c>
-      <c r="C109" s="13" t="n">
-        <v>2433.674</v>
+          <t>Base probability</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — P/BV</t>
-        </is>
-      </c>
-      <c r="C110" s="23">
-        <f>MAX(0,$C$108*$C$109/$C$77*$C$85*$C$78)</f>
-        <v/>
+          <t>Bull probability</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Bull 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>1519.911066708556</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>TARGET</t>
-        </is>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Probability-weighted 12-month value</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>$C$107*$C$108+$C$109*$C$106+$C$110*$C$111</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Weight: Sum of the parts</t>
+          <t>Liquidity discount (limits.yaml)</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Weight: P/E</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>0.25</v>
+          <t>Fundamental 12-month value (after liquidity discount)</t>
+        </is>
+      </c>
+      <c r="C114" s="23">
+        <f>$C$112*(1-$C$113)</f>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Weight: P/BV</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>0.15</v>
+          <t>Konglo lens: price / fundamental value today (engine)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n">
+        <v>1.084244</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Value today (weighted)</t>
-        </is>
-      </c>
-      <c r="C116" s="23">
-        <f>$C$100*$C$113+$C$105*$C$114+$C$110*$C$115</f>
-        <v/>
+          <t>Regime bear: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DPS expected in next 12 months (IDR)</t>
-        </is>
-      </c>
-      <c r="C117" s="15" t="n">
-        <v>16.5827941436435</v>
+          <t>Regime bear: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Base-case 12-month value</t>
-        </is>
-      </c>
-      <c r="C118" s="23">
-        <f>MAX(0,$C$116*(1+$C$94)-$C$117)</f>
-        <v/>
+          <t>Regime base: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bear probability</t>
+          <t>Regime base: share of the log gap closed in 12 months</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bear 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>1293.368451285954</v>
+          <t>Regime bull: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Base probability</t>
+          <t>Regime bull: share of the log gap closed in 12 months</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.5</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bull probability</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>0.25</v>
+          <t>Share of today's premium kept (probability-weighted)</t>
+        </is>
+      </c>
+      <c r="C122" s="27">
+        <f>$C$116*$C$115^(1-$C$117)+$C$118*$C$115^(1-$C$119)+$C$120*$C$115^(1-$C$121)</f>
+        <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bull 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n">
-        <v>1519.431380258833</v>
+          <t>TARGET PRICE (IDR) — konglo lens</t>
+        </is>
+      </c>
+      <c r="C123" s="24">
+        <f>$C$114*$C$122</f>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Probability-weighted 12-month value</t>
-        </is>
-      </c>
-      <c r="C124" s="23">
-        <f>$C$119*$C$120+$C$121*$C$118+$C$122*$C$123</f>
+          <t>Expected 12-month total return</t>
+        </is>
+      </c>
+      <c r="C124" s="25">
+        <f>($C$123+$C$105)/$C$76-1</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Liquidity discount (limits.yaml)</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Fundamental 12-month value (after liquidity discount)</t>
-        </is>
-      </c>
-      <c r="C126" s="23">
-        <f>$C$124*(1-$C$125)</f>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C125" s="26">
+        <f>IF($C$124&gt;=0.25,"BUY",IF($C$124&gt;=0.1,"ADD",IF($C$124&lt;=-0.25,"SELL",IF($C$124&lt;=-0.1,"REDUCE","HOLD"))))</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Konglo lens: price / fundamental value today (engine)</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="n">
-        <v>1.151266</v>
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Regime bear: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>0.25</v>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H128" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Regime bear: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>0.7</v>
+      <c r="C129" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>1509.063596</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>1414.413539</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>1319.763482</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <v>1225.113426</v>
+      </c>
+      <c r="H129" s="23" t="n">
+        <v>1130.463369</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Regime base: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>0.5</v>
+      <c r="C130" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D130" s="23" t="n">
+        <v>1515.572411</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>1420.515553</v>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>1325.458696</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <v>1230.401838</v>
+      </c>
+      <c r="H130" s="23" t="n">
+        <v>1135.344981</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Regime base: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>0.3</v>
+      <c r="C131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="23" t="n">
+        <v>1522.081226</v>
+      </c>
+      <c r="E131" s="23" t="n">
+        <v>1426.617568</v>
+      </c>
+      <c r="F131" s="23" t="n">
+        <v>1331.153909</v>
+      </c>
+      <c r="G131" s="23" t="n">
+        <v>1235.690251</v>
+      </c>
+      <c r="H131" s="23" t="n">
+        <v>1140.226592</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Regime bull: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>0.25</v>
+      <c r="C132" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>1528.590042</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>1432.719582</v>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>1336.849123</v>
+      </c>
+      <c r="G132" s="23" t="n">
+        <v>1240.978663</v>
+      </c>
+      <c r="H132" s="23" t="n">
+        <v>1145.108204</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Regime bull: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Share of today's premium kept (probability-weighted)</t>
-        </is>
-      </c>
-      <c r="C134" s="27">
-        <f>$C$128*$C$127^(1-$C$129)+$C$130*$C$127^(1-$C$131)+$C$132*$C$127^(1-$C$133)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>TARGET PRICE (IDR) — konglo lens</t>
-        </is>
-      </c>
-      <c r="C135" s="24">
-        <f>$C$126*$C$134</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Expected 12-month total return</t>
-        </is>
-      </c>
-      <c r="C136" s="25">
-        <f>($C$135+$C$117)/$C$76-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="C137" s="26">
-        <f>IF($C$136&gt;=0.25,"BUY",IF($C$136&gt;=0.1,"ADD",IF($C$136&lt;=-0.25,"SELL",IF($C$136&lt;=-0.1,"REDUCE","HOLD"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E140" s="1" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F140" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H140" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="C141" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D141" s="23" t="n">
-        <v>1507.054332</v>
-      </c>
-      <c r="E141" s="23" t="n">
-        <v>1450.625146</v>
-      </c>
-      <c r="F141" s="23" t="n">
-        <v>1394.195961</v>
-      </c>
-      <c r="G141" s="23" t="n">
-        <v>1337.766775</v>
-      </c>
-      <c r="H141" s="23" t="n">
-        <v>1281.337589</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142" s="1" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D142" s="23" t="n">
-        <v>1513.644451</v>
-      </c>
-      <c r="E142" s="23" t="n">
-        <v>1456.971194</v>
-      </c>
-      <c r="F142" s="23" t="n">
-        <v>1400.297938</v>
-      </c>
-      <c r="G142" s="23" t="n">
-        <v>1343.624682</v>
-      </c>
-      <c r="H142" s="23" t="n">
-        <v>1286.951426</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="C143" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="23" t="n">
-        <v>1520.234569</v>
-      </c>
-      <c r="E143" s="23" t="n">
-        <v>1463.317243</v>
-      </c>
-      <c r="F143" s="23" t="n">
-        <v>1406.399916</v>
-      </c>
-      <c r="G143" s="23" t="n">
-        <v>1349.482589</v>
-      </c>
-      <c r="H143" s="23" t="n">
-        <v>1292.565262</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="C144" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D144" s="23" t="n">
-        <v>1526.824688</v>
-      </c>
-      <c r="E144" s="23" t="n">
-        <v>1469.663291</v>
-      </c>
-      <c r="F144" s="23" t="n">
-        <v>1412.501893</v>
-      </c>
-      <c r="G144" s="23" t="n">
-        <v>1355.340496</v>
-      </c>
-      <c r="H144" s="23" t="n">
-        <v>1298.179098</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="C145" s="1" t="n">
+      <c r="C133" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="D145" s="23" t="n">
-        <v>1533.414807</v>
-      </c>
-      <c r="E145" s="23" t="n">
-        <v>1476.009339</v>
-      </c>
-      <c r="F145" s="23" t="n">
-        <v>1418.603871</v>
-      </c>
-      <c r="G145" s="23" t="n">
-        <v>1361.198403</v>
-      </c>
-      <c r="H145" s="23" t="n">
-        <v>1303.792935</v>
+      <c r="D133" s="23" t="n">
+        <v>1535.098857</v>
+      </c>
+      <c r="E133" s="23" t="n">
+        <v>1438.821596</v>
+      </c>
+      <c r="F133" s="23" t="n">
+        <v>1342.544336</v>
+      </c>
+      <c r="G133" s="23" t="n">
+        <v>1246.267075</v>
+      </c>
+      <c r="H133" s="23" t="n">
+        <v>1149.989815</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T01:56:00+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T10:26:45+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
         <v>1.936368769775187e-05</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>0.00017791</v>
+        <v>1.7791e-05</v>
       </c>
       <c r="H46" s="16">
         <f>(MAX(H45,0)*H23)</f>
@@ -4075,7 +4075,7 @@
         <v>0.01353885294601361</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.148628166630749</v>
+        <v>0.0148628166630749</v>
       </c>
       <c r="H72" s="17">
         <f>IF(H45=0,0,H46/H45)</f>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4555132137760979</v>
+        <v>0.4555886090666539</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.187121</v>
+        <v>39.193607</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.848106</v>
+        <v>0.847966</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005902394683170218</v>
+        <v>0.005903371631255709</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.65791260589593</v>
+        <v>38.65620650668208</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>52.87364411030559</v>
+        <v>52.87159337014091</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.447929</v>
+        <v>12.446271</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.732888</v>
+        <v>50.730928</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.116465</v>
+        <v>48.114531</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.500042</v>
+        <v>45.498133</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>42.883619</v>
+        <v>42.881735</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.267197</v>
+        <v>40.265338</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>50.959059</v>
+        <v>50.95713</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.330973</v>
+        <v>48.329067</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.702887</v>
+        <v>45.701005</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.074802</v>
+        <v>43.072943</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.446716</v>
+        <v>40.44488</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.185229</v>
+        <v>51.183331</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.545481</v>
+        <v>48.543604</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>45.905732</v>
+        <v>45.903877</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.265984</v>
+        <v>43.26415</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.626235</v>
+        <v>40.624423</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.4114</v>
+        <v>51.409533</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.759989</v>
+        <v>48.758141</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.108577</v>
+        <v>46.106749</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.457166</v>
+        <v>43.455357</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.805755</v>
+        <v>40.803965</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.637571</v>
+        <v>51.635734</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>48.974497</v>
+        <v>48.972678</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.311422</v>
+        <v>46.309621</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.648348</v>
+        <v>43.646564</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>40.985274</v>
+        <v>40.983508</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4884,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.066581</v>
+        <v>0.058676</v>
       </c>
     </row>
     <row r="19">
@@ -5382,34 +5382,34 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0</v>
+        <v>44.157</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0</v>
+        <v>44.157</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0</v>
+        <v>44.157</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>44.157</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>44.157</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>0</v>
+        <v>45.04013999999999</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>0</v>
+        <v>45.94094279999999</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0</v>
+        <v>46.859761656</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>47.79695688912</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>48.7528960269024</v>
       </c>
     </row>
     <row r="22">
@@ -5424,34 +5424,34 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.43326</v>
+        <v>0.361755</v>
       </c>
     </row>
     <row r="23">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2984847707170161</v>
+        <v>0.298534175092859</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>207.865779</v>
+        <v>215.912256</v>
       </c>
     </row>
     <row r="102">
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="108">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>200.3204853322435</v>
+        <v>208.0382999605944</v>
       </c>
     </row>
     <row r="109">
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="110">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>267.0939804429914</v>
+        <v>277.3843999474593</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.608098</v>
+        <v>3.498623</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>264.718372</v>
+        <v>274.916831</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>248.173473</v>
+        <v>257.734529</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>231.628575</v>
+        <v>240.552227</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>215.083677</v>
+        <v>223.369925</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>198.538779</v>
+        <v>206.187623</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>265.906176</v>
+        <v>276.150616</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>249.28704</v>
+        <v>258.891202</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>232.667904</v>
+        <v>241.631789</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>216.048768</v>
+        <v>224.372375</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>199.429632</v>
+        <v>207.112962</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>267.09398</v>
+        <v>277.3844</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>250.400607</v>
+        <v>260.047875</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>233.707233</v>
+        <v>242.71135</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>217.013859</v>
+        <v>225.374825</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>200.320485</v>
+        <v>208.0383</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>268.281785</v>
+        <v>278.618184</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>251.514173</v>
+        <v>261.204548</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>234.746562</v>
+        <v>243.790911</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>217.97895</v>
+        <v>226.377275</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>201.211339</v>
+        <v>208.963638</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>269.469589</v>
+        <v>279.851969</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>252.62774</v>
+        <v>262.361221</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>235.785891</v>
+        <v>244.870473</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>218.944041</v>
+        <v>227.379724</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>202.102192</v>
+        <v>209.888976</v>
       </c>
     </row>
   </sheetData>
@@ -9065,7 +9065,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -13153,7 +13153,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -17299,7 +17299,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.674736225649127</v>
+        <v>1.675013423369234</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.071475</v>
+        <v>150.096314</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.848106</v>
+        <v>0.847966</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.477397</v>
+        <v>15.475456</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.4980721222381</v>
+        <v>289.460463794096</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.0856909918504</v>
+        <v>320.0483342528154</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.393524</v>
+        <v>317.356058</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>309.810936</v>
+        <v>309.773418</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.228348</v>
+        <v>302.190777</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.645759</v>
+        <v>294.608136</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.063171</v>
+        <v>287.025496</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>318.739608</v>
+        <v>318.702196</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.124861</v>
+        <v>311.087392</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.510115</v>
+        <v>303.472588</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>295.895368</v>
+        <v>295.857784</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.280621</v>
+        <v>288.24298</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.085691</v>
+        <v>320.048334</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.438786</v>
+        <v>312.401367</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>304.791882</v>
+        <v>304.754399</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.144977</v>
+        <v>297.107431</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.498072</v>
+        <v>289.460464</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.431774</v>
+        <v>321.394472</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>313.752711</v>
+        <v>313.715341</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.073649</v>
+        <v>306.03621</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.394586</v>
+        <v>298.357079</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.715523</v>
+        <v>290.677948</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>322.777858</v>
+        <v>322.74061</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.066637</v>
+        <v>315.029316</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.355416</v>
+        <v>307.318021</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.644194</v>
+        <v>299.606726</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>291.932973</v>
+        <v>291.895432</v>
       </c>
     </row>
   </sheetData>
@@ -21492,7 +21492,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.05009</v>
+        <v>0.04989</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25700,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.164928</v>
+        <v>5.164074</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.92505</v>
+        <v>3.924798</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041104</v>
+        <v>0.041111</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.333663</v>
+        <v>8.332284</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.420335</v>
+        <v>4.419569</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.119947</v>
+        <v>0.119967</v>
       </c>
     </row>
     <row r="4">
@@ -26068,10 +26068,10 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>23.138996</v>
+        <v>23.135166</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>7.889215</v>
+        <v>7.888708</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>0.004322</v>
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1711.16988</v>
+        <v>1710.886698</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.424926</v>
+        <v>14.365857</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.2e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>38.960107</v>
+        <v>30.177229</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.698809</v>
+        <v>15.616347</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.728541</v>
+        <v>10.727819</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -26344,7 +26344,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2545.240717</v>
+        <v>2545.397898</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.4045434566658</v>
+        <v>104.4218242086862</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2537.868562546187</v>
+        <v>2537.715452041602</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3627.541116021459</v>
+        <v>3627.274312595048</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3596.550748</v>
+        <v>3596.280869</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3326.394791</v>
+        <v>3326.153475</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3056.238834</v>
+        <v>3056.026081</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2786.082877</v>
+        <v>2785.898687</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2515.92692</v>
+        <v>2515.771293</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3612.045932</v>
+        <v>3611.777591</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3340.758884</v>
+        <v>3340.519036</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3069.471837</v>
+        <v>3069.260482</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2798.184789</v>
+        <v>2798.001927</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2526.897741</v>
+        <v>2526.743373</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3627.541116</v>
+        <v>3627.274313</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3355.122978</v>
+        <v>3354.884597</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3082.704839</v>
+        <v>3082.494882</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2810.286701</v>
+        <v>2810.105167</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2537.868563</v>
+        <v>2537.715452</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3643.0363</v>
+        <v>3642.771034</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3369.487071</v>
+        <v>3369.250159</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3095.937842</v>
+        <v>3095.729283</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2822.388613</v>
+        <v>2822.208407</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2548.839384</v>
+        <v>2548.687531</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3658.531484</v>
+        <v>3658.267756</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3383.851164</v>
+        <v>3383.61572</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3109.170844</v>
+        <v>3108.963683</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2834.490525</v>
+        <v>2834.311647</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2559.810205</v>
+        <v>2559.659611</v>
       </c>
     </row>
   </sheetData>
@@ -30537,7 +30537,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4961439182752081</v>
+        <v>0.4962260386478881</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2386.428322</v>
+        <v>2386.640882</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>295.0702536897418</v>
+        <v>295.1190929041456</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1873.024682883861</v>
+        <v>1872.854424924326</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2322.168225238017</v>
+        <v>2321.956605770986</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2306.323337</v>
+        <v>2306.110346</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2191.406504</v>
+        <v>2191.203339</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2076.48967</v>
+        <v>2076.296333</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1961.572837</v>
+        <v>1961.389326</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1846.656003</v>
+        <v>1846.482319</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2317.899484</v>
+        <v>2317.687784</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2202.471273</v>
+        <v>2202.269354</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2087.043062</v>
+        <v>2086.850924</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1971.614851</v>
+        <v>1971.432494</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1856.18664</v>
+        <v>1856.014064</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2329.475631</v>
+        <v>2329.265221</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2213.536043</v>
+        <v>2213.335368</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2097.596454</v>
+        <v>2097.405515</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1981.656866</v>
+        <v>1981.475663</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1865.717277</v>
+        <v>1865.54581</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2341.051778</v>
+        <v>2340.842658</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2224.600812</v>
+        <v>2224.401383</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2108.149846</v>
+        <v>2107.960107</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1991.69888</v>
+        <v>1991.518831</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1875.247914</v>
+        <v>1875.077555</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2352.627925</v>
+        <v>2352.420096</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2235.665581</v>
+        <v>2235.467397</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2118.703238</v>
+        <v>2118.514698</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2001.740894</v>
+        <v>2001.561999</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1884.778551</v>
+        <v>1884.6093</v>
       </c>
     </row>
   </sheetData>
@@ -34730,7 +34730,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-26</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -38906,7 +38906,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -43092,7 +43092,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.952961</v>
+        <v>1.952637</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.89123151369081</v>
+        <v>30.88874474554688</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>36.99297018393752</v>
+        <v>36.99048341579359</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.821757</v>
+        <v>1.821893</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.683688</v>
+        <v>36.681222</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.171006</v>
+        <v>35.168541</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.658325</v>
+        <v>33.655859</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.145644</v>
+        <v>32.143178</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.632963</v>
+        <v>30.630497</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.838329</v>
+        <v>36.835853</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.319271</v>
+        <v>35.316795</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.800213</v>
+        <v>33.797737</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.281155</v>
+        <v>32.278679</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.762097</v>
+        <v>30.759621</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>36.99297</v>
+        <v>36.990483</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.467536</v>
+        <v>35.465049</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.942101</v>
+        <v>33.939614</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.416666</v>
+        <v>32.414179</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.891232</v>
+        <v>30.888745</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.147611</v>
+        <v>37.145114</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.6158</v>
+        <v>35.613303</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.083989</v>
+        <v>34.081491</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.552177</v>
+        <v>32.54968</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>31.020366</v>
+        <v>31.017869</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.302253</v>
+        <v>37.299745</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.764065</v>
+        <v>35.761557</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.225876</v>
+        <v>34.223369</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.687688</v>
+        <v>32.685181</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.1495</v>
+        <v>31.146992</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18125</v>
+        <v>18128</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.342439132506286</v>
+        <v>1.342661329328218</v>
       </c>
     </row>
     <row r="92">
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>1139.042678</v>
+        <v>1095.301015</v>
       </c>
     </row>
     <row r="102">
@@ -51143,7 +51143,7 @@
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>5.337310312020393</v>
+        <v>5.338193728899624</v>
       </c>
     </row>
     <row r="106">
@@ -51174,7 +51174,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>1142.316793508954</v>
+        <v>1098.146194977824</v>
       </c>
     </row>
     <row r="109">
@@ -51204,7 +51204,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>1519.911066708556</v>
+        <v>1461.016409321363</v>
       </c>
     </row>
     <row r="112">
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>1.084244</v>
+        <v>1.127544</v>
       </c>
     </row>
     <row r="116">
@@ -51387,19 +51387,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>1509.063596</v>
+        <v>1450.669202</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>1414.413539</v>
+        <v>1359.66874</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1319.763482</v>
+        <v>1268.668278</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>1225.113426</v>
+        <v>1177.667815</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>1130.463369</v>
+        <v>1086.667353</v>
       </c>
     </row>
     <row r="130">
@@ -51407,19 +51407,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>1515.572411</v>
+        <v>1456.928065</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>1420.515553</v>
+        <v>1365.536424</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>1325.458696</v>
+        <v>1274.144783</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>1230.401838</v>
+        <v>1182.753142</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>1135.344981</v>
+        <v>1091.3615</v>
       </c>
     </row>
     <row r="131">
@@ -51427,19 +51427,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>1522.081226</v>
+        <v>1463.186928</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>1426.617568</v>
+        <v>1371.404108</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>1331.153909</v>
+        <v>1279.621288</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1235.690251</v>
+        <v>1187.838468</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>1140.226592</v>
+        <v>1096.055648</v>
       </c>
     </row>
     <row r="132">
@@ -51447,19 +51447,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>1528.590042</v>
+        <v>1469.445791</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>1432.719582</v>
+        <v>1377.271792</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>1336.849123</v>
+        <v>1285.097793</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1240.978663</v>
+        <v>1192.923794</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1145.108204</v>
+        <v>1100.749795</v>
       </c>
     </row>
     <row r="133">
@@ -51467,19 +51467,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>1535.098857</v>
+        <v>1475.704654</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>1438.821596</v>
+        <v>1383.139476</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>1342.544336</v>
+        <v>1290.574298</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1246.267075</v>
+        <v>1198.00912</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1149.989815</v>
+        <v>1105.443942</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T10:26:45+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T12:32:24+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1618,10 +1618,10 @@
         <v>20.992</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>26.611</v>
+        <v>20.04</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>25.324</v>
+        <v>45.378</v>
       </c>
       <c r="H33" s="14">
         <f>(H31-H32)</f>
@@ -1746,10 +1746,10 @@
         <v>21.005</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>126.468</v>
+        <v>119.897</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>180.642</v>
+        <v>200.696</v>
       </c>
       <c r="H35" s="14">
         <f>(H33+H34)</f>
@@ -1938,10 +1938,10 @@
         <v>-1.568</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>186.798</v>
+        <v>193.369</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>213.755</v>
+        <v>193.701</v>
       </c>
       <c r="H38" s="14">
         <f>H21</f>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>1.936368769775187e-05</v>
+        <v>1.952740336958144e-05</v>
       </c>
       <c r="G46" s="15" t="n">
         <v>1.7791e-05</v>
@@ -2698,10 +2698,10 @@
         <v>-52.54393281600981</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>-90.90747433348928</v>
+        <v>-97.43736716557534</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>-267.9576974609766</v>
+        <v>-247.5376014604407</v>
       </c>
       <c r="H50" s="14">
         <f>((((H33*(1-H17))+H34)-H48)-H49)</f>
@@ -3694,10 +3694,10 @@
         <v>0.2144614724891008</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.1577452561545571</v>
+        <v>0.1495491584998809</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.1486009585247998</v>
+        <v>0.165097917273354</v>
       </c>
       <c r="H66" s="17">
         <f>IF(H29=0,0,H35/H29)</f>
@@ -3758,10 +3758,10 @@
         <v>0.2143287422276222</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0.03319226216536136</v>
+        <v>0.02499616451068511</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.02083220222142153</v>
+        <v>0.03732916096997577</v>
       </c>
       <c r="H67" s="17">
         <f>IF(H29=0,0,H33/H29)</f>
@@ -4010,10 +4010,10 @@
         <v>0.621471078314687</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>4.050123351361609</v>
+        <v>4.272091878862691</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>5.507844244417134</v>
+        <v>4.957487941961972</v>
       </c>
       <c r="H71" s="19">
         <f>IF(H35=0,0,H62/H35)</f>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.01353885294601361</v>
+        <v>0.01365332093581266</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>0.0148628166630749</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>505</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4555886090666539</v>
+        <v>0.6023498184811887</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.193607</v>
+        <v>39.197931</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847966</v>
+        <v>0.847872</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005903371631255709</v>
+        <v>0.005904022929979369</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.65620650668208</v>
+        <v>38.89090377523001</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>52.87159337014091</v>
+        <v>53.20438329862506</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>12.446271</v>
+        <v>9.413967</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>50.730928</v>
+        <v>51.047392</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.114531</v>
+        <v>48.414624</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.498133</v>
+        <v>45.781856</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>42.881735</v>
+        <v>43.149088</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.265338</v>
+        <v>40.51632</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>50.95713</v>
+        <v>51.273614</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.329067</v>
+        <v>48.62918</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.701005</v>
+        <v>45.984746</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.072943</v>
+        <v>43.340312</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.44488</v>
+        <v>40.695878</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.183331</v>
+        <v>51.499836</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.543604</v>
+        <v>48.843736</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>45.903877</v>
+        <v>46.187636</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.26415</v>
+        <v>43.531536</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.624423</v>
+        <v>40.875436</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.409533</v>
+        <v>51.726058</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>48.758141</v>
+        <v>49.058292</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.106749</v>
+        <v>46.390526</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.455357</v>
+        <v>43.72276</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>40.803965</v>
+        <v>41.054994</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.635734</v>
+        <v>51.95228</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>48.972678</v>
+        <v>49.272848</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.309621</v>
+        <v>46.593416</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.646564</v>
+        <v>43.913984</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>40.983508</v>
+        <v>41.234552</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4884,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>750</v>
+        <v>675</v>
       </c>
     </row>
     <row r="77">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.298534175092859</v>
+        <v>0.3317412348260231</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>215.912256</v>
+        <v>215.928849</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>208.0382999605944</v>
+        <v>208.3429286022706</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>277.3843999474593</v>
+        <v>277.7905714696942</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.498623</v>
+        <v>3.148519</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>274.916831</v>
+        <v>275.322813</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>257.734529</v>
+        <v>258.115137</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>240.552227</v>
+        <v>240.907462</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>223.369925</v>
+        <v>223.699786</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>206.187623</v>
+        <v>206.49211</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>276.150616</v>
+        <v>276.556692</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>258.891202</v>
+        <v>259.271899</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>241.631789</v>
+        <v>241.987106</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>224.372375</v>
+        <v>224.702313</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>207.112962</v>
+        <v>207.417519</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>277.3844</v>
+        <v>277.790571</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>260.047875</v>
+        <v>260.428661</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>242.71135</v>
+        <v>243.06675</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>225.374825</v>
+        <v>225.704839</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>208.0383</v>
+        <v>208.342929</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>278.618184</v>
+        <v>279.024451</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>261.204548</v>
+        <v>261.585422</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>243.790911</v>
+        <v>244.146394</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>226.377275</v>
+        <v>226.707366</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>208.963638</v>
+        <v>209.268338</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>279.851969</v>
+        <v>280.25833</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>262.361221</v>
+        <v>262.742184</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>244.870473</v>
+        <v>245.226039</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>227.379724</v>
+        <v>227.709893</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>209.888976</v>
+        <v>210.193747</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.675013423369234</v>
+        <v>1.675198221849306</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.096314</v>
+        <v>150.112874</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847966</v>
+        <v>0.847872</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>15.475456</v>
+        <v>14.301321</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>289.460463794096</v>
+        <v>276.3361087657509</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>320.0483342528154</v>
+        <v>306.9275772172747</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>317.356058</v>
+        <v>304.345693</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>309.773418</v>
+        <v>296.76216</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>302.190777</v>
+        <v>289.178627</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>294.608136</v>
+        <v>281.595094</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>287.025496</v>
+        <v>274.011561</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>318.702196</v>
+        <v>305.636635</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>311.087392</v>
+        <v>298.020935</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>303.472588</v>
+        <v>290.405235</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>295.857784</v>
+        <v>282.789535</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>288.24298</v>
+        <v>275.173835</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>320.048334</v>
+        <v>306.927577</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>312.401367</v>
+        <v>299.27971</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>304.754399</v>
+        <v>291.631843</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>297.107431</v>
+        <v>283.983976</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>289.460464</v>
+        <v>276.336109</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>321.394472</v>
+        <v>308.218519</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>313.715341</v>
+        <v>300.538485</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>306.03621</v>
+        <v>292.858451</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>298.357079</v>
+        <v>285.178417</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>290.677948</v>
+        <v>277.498383</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>322.74061</v>
+        <v>309.509461</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>315.029316</v>
+        <v>301.79726</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>307.318021</v>
+        <v>294.085059</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>299.606726</v>
+        <v>286.372858</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>291.895432</v>
+        <v>278.660656</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.164074</v>
+        <v>5.163504</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.924798</v>
+        <v>3.924631</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041111</v>
+        <v>0.041115</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.332284</v>
+        <v>8.331365</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.419569</v>
+        <v>4.419058</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.119967</v>
+        <v>0.11998</v>
       </c>
     </row>
     <row r="4">
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>23.135166</v>
+        <v>23.132614</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>7.888708</v>
+        <v>7.888371</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.004322</v>
+        <v>0.004323</v>
       </c>
     </row>
     <row r="8">
@@ -26109,13 +26109,13 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1710.886698</v>
+        <v>1294.032915</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.365857</v>
+        <v>11.932453</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.2e-05</v>
+        <v>1.5e-05</v>
       </c>
     </row>
     <row r="9">
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>30.177229</v>
+        <v>27.15651</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>15.616347</v>
+        <v>14.400412</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.727819</v>
+        <v>10.727337</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2545.397898</v>
+        <v>2545.502686</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.4218242086862</v>
+        <v>104.4333447100331</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2537.715452041602</v>
+        <v>2537.905933600475</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3627.274312595048</v>
+        <v>3627.509648552048</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3596.280869</v>
+        <v>3596.514155</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3326.153475</v>
+        <v>3326.37564</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3056.026081</v>
+        <v>3056.237126</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2785.898687</v>
+        <v>2786.098612</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2515.771293</v>
+        <v>2515.960097</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3611.777591</v>
+        <v>3612.011902</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3340.519036</v>
+        <v>3340.74218</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3069.260482</v>
+        <v>3069.472459</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2798.001927</v>
+        <v>2798.202737</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2526.743373</v>
+        <v>2526.933015</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3627.274313</v>
+        <v>3627.509649</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3354.884597</v>
+        <v>3355.10872</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3082.494882</v>
+        <v>3082.707791</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2810.105167</v>
+        <v>2810.306862</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2537.715452</v>
+        <v>2537.905934</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3642.771034</v>
+        <v>3643.007395</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3369.250159</v>
+        <v>3369.47526</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3095.729283</v>
+        <v>3095.943124</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2822.208407</v>
+        <v>2822.410988</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2548.687531</v>
+        <v>2548.878852</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3658.267756</v>
+        <v>3658.505142</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3383.61572</v>
+        <v>3383.841799</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3108.963683</v>
+        <v>3109.178456</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2834.311647</v>
+        <v>2834.515113</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2559.659611</v>
+        <v>2559.85177</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4962260386478881</v>
+        <v>0.4962807855630081</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2386.640882</v>
+        <v>2386.78259</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>295.1190929041456</v>
+        <v>295.1516523804149</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1872.854424924326</v>
+        <v>1872.995070885319</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2321.956605770986</v>
+        <v>2322.124224482865</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2306.110346</v>
+        <v>2306.27705</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2191.203339</v>
+        <v>2191.362958</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2076.296333</v>
+        <v>2076.448866</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1961.389326</v>
+        <v>1961.534773</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1846.482319</v>
+        <v>1846.620681</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2317.687784</v>
+        <v>2317.855348</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2202.269354</v>
+        <v>2202.429802</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2086.850924</v>
+        <v>2087.004257</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1971.432494</v>
+        <v>1971.578711</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1856.014064</v>
+        <v>1856.153165</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2329.265221</v>
+        <v>2329.433646</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2213.335368</v>
+        <v>2213.496647</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2097.405515</v>
+        <v>2097.559648</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1981.475663</v>
+        <v>1981.622649</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1865.54581</v>
+        <v>1865.685649</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2340.842658</v>
+        <v>2341.011944</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2224.401383</v>
+        <v>2224.563491</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2107.960107</v>
+        <v>2108.115039</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1991.518831</v>
+        <v>1991.666586</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1875.077555</v>
+        <v>1875.218134</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2352.420096</v>
+        <v>2352.590242</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2235.467397</v>
+        <v>2235.630336</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2118.514698</v>
+        <v>2118.67043</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2001.561999</v>
+        <v>2001.710524</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1884.6093</v>
+        <v>1884.750618</v>
       </c>
     </row>
   </sheetData>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.952637</v>
+        <v>1.799573</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.88874474554688</v>
+        <v>29.71102080950602</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>36.99048341579359</v>
+        <v>35.81275947975273</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.821893</v>
+        <v>1.888314</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>36.681222</v>
+        <v>35.513344</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>35.168541</v>
+        <v>34.000663</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>33.655859</v>
+        <v>32.487982</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>32.143178</v>
+        <v>30.975301</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>30.630497</v>
+        <v>29.46262</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.835853</v>
+        <v>35.663052</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>35.316795</v>
+        <v>34.143994</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>33.797737</v>
+        <v>32.624936</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>32.278679</v>
+        <v>31.105878</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>30.759621</v>
+        <v>29.58682</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>36.990483</v>
+        <v>35.812759</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>35.465049</v>
+        <v>34.287325</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.939614</v>
+        <v>32.76189</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>32.414179</v>
+        <v>31.236455</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.888745</v>
+        <v>29.711021</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>37.145114</v>
+        <v>35.962467</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>35.613303</v>
+        <v>34.430656</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>34.081491</v>
+        <v>32.898844</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>32.54968</v>
+        <v>31.367033</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>31.017869</v>
+        <v>29.835221</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>37.299745</v>
+        <v>36.112175</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>35.761557</v>
+        <v>34.573987</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>34.223369</v>
+        <v>33.035798</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>32.685181</v>
+        <v>31.49761</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>31.146992</v>
+        <v>29.959422</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18128</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.342661329328218</v>
+        <v>1.342809460542839</v>
       </c>
     </row>
     <row r="92">
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>1095.301015</v>
+        <v>961.794291</v>
       </c>
     </row>
     <row r="102">
@@ -51143,7 +51143,7 @@
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>5.338193728899624</v>
+        <v>5.338782673485778</v>
       </c>
     </row>
     <row r="106">
@@ -51174,7 +51174,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>1098.146194977824</v>
+        <v>963.9021906533591</v>
       </c>
     </row>
     <row r="109">
@@ -51204,7 +51204,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>1461.016409321363</v>
+        <v>1282.024052880507</v>
       </c>
     </row>
     <row r="112">
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>1.127544</v>
+        <v>1.284058</v>
       </c>
     </row>
     <row r="116">
@@ -51387,19 +51387,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>1450.669202</v>
+        <v>1273.202876</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>1359.66874</v>
+        <v>1193.294023</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1268.668278</v>
+        <v>1113.385169</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>1177.667815</v>
+        <v>1033.476315</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>1086.667353</v>
+        <v>953.567462</v>
       </c>
     </row>
     <row r="130">
@@ -51407,19 +51407,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>1456.928065</v>
+        <v>1278.698844</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>1365.536424</v>
+        <v>1198.446492</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>1274.144783</v>
+        <v>1118.19414</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>1182.753142</v>
+        <v>1037.941789</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>1091.3615</v>
+        <v>957.689437</v>
       </c>
     </row>
     <row r="131">
@@ -51427,19 +51427,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>1463.186928</v>
+        <v>1284.194811</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>1371.404108</v>
+        <v>1203.598961</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>1279.621288</v>
+        <v>1123.003112</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1187.838468</v>
+        <v>1042.407262</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>1096.055648</v>
+        <v>961.811413</v>
       </c>
     </row>
     <row r="132">
@@ -51447,19 +51447,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>1469.445791</v>
+        <v>1289.690778</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>1377.271792</v>
+        <v>1208.751431</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>1285.097793</v>
+        <v>1127.812083</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1192.923794</v>
+        <v>1046.872736</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1100.749795</v>
+        <v>965.933388</v>
       </c>
     </row>
     <row r="133">
@@ -51467,19 +51467,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>1475.704654</v>
+        <v>1295.186746</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>1383.139476</v>
+        <v>1213.9039</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>1290.574298</v>
+        <v>1132.621055</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1198.00912</v>
+        <v>1051.338209</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1105.443942</v>
+        <v>970.0553640000001</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T12:32:24+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T19:34:52+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.6023498184811887</v>
+        <v>0.6026156099068838</v>
       </c>
     </row>
     <row r="92">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>39.197931</v>
+        <v>39.215227</v>
       </c>
     </row>
     <row r="102">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847872</v>
+        <v>0.847498</v>
       </c>
     </row>
     <row r="104">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.005904022929979369</v>
+        <v>0.00590662812487401</v>
       </c>
     </row>
     <row r="112">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.89090377523001</v>
+        <v>38.90443922301376</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>53.20438329862506</v>
+        <v>53.22454916970256</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>9.413967</v>
+        <v>9.410624</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>51.047392</v>
+        <v>51.066542</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.414624</v>
+        <v>48.432583</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.781856</v>
+        <v>45.798624</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>43.149088</v>
+        <v>43.164666</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.51632</v>
+        <v>40.530707</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>51.273614</v>
+        <v>51.292846</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.62918</v>
+        <v>48.647216</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>45.984746</v>
+        <v>46.001586</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.340312</v>
+        <v>43.355957</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.695878</v>
+        <v>40.710327</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.499836</v>
+        <v>51.519151</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.843736</v>
+        <v>48.86185</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>46.187636</v>
+        <v>46.204549</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.531536</v>
+        <v>43.547247</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.875436</v>
+        <v>40.889946</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.726058</v>
+        <v>51.745455</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>49.058292</v>
+        <v>49.076483</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.390526</v>
+        <v>46.407511</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.72276</v>
+        <v>43.738538</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>41.054994</v>
+        <v>41.069566</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.95228</v>
+        <v>51.97176</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>49.272848</v>
+        <v>49.291116</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.593416</v>
+        <v>46.610473</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.913984</v>
+        <v>43.929829</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>41.234552</v>
+        <v>41.249186</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.3317412348260231</v>
+        <v>0.3318876181618537</v>
       </c>
     </row>
     <row r="92">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>215.928849</v>
+        <v>215.983721</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>208.3429286022706</v>
+        <v>208.3971453533571</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>277.7905714696942</v>
+        <v>277.8628604711428</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.148519</v>
+        <v>3.147719</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>275.322813</v>
+        <v>275.394475</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>258.115137</v>
+        <v>258.18232</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>240.907462</v>
+        <v>240.970166</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>223.699786</v>
+        <v>223.758011</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>206.49211</v>
+        <v>206.545856</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>276.556692</v>
+        <v>276.628668</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>259.271899</v>
+        <v>259.339376</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>241.987106</v>
+        <v>242.050084</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>224.702313</v>
+        <v>224.760793</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>207.417519</v>
+        <v>207.471501</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>277.790571</v>
+        <v>277.86286</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>260.428661</v>
+        <v>260.496432</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>243.06675</v>
+        <v>243.130003</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>225.704839</v>
+        <v>225.763574</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>208.342929</v>
+        <v>208.397145</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>279.024451</v>
+        <v>279.097053</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>261.585422</v>
+        <v>261.653487</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>244.146394</v>
+        <v>244.209922</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>226.707366</v>
+        <v>226.766356</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>209.268338</v>
+        <v>209.32279</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>280.25833</v>
+        <v>280.331246</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>262.742184</v>
+        <v>262.810543</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>245.226039</v>
+        <v>245.28984</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>227.709893</v>
+        <v>227.769137</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>210.193747</v>
+        <v>210.248434</v>
       </c>
     </row>
   </sheetData>
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.675198221849306</v>
+        <v>1.675937415769593</v>
       </c>
     </row>
     <row r="92">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.112874</v>
+        <v>150.179112</v>
       </c>
     </row>
     <row r="102">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847872</v>
+        <v>0.847498</v>
       </c>
     </row>
     <row r="104">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="C108" s="18" t="n">
-        <v>14.301321</v>
+        <v>14.296665</v>
       </c>
     </row>
     <row r="109">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>276.3361087657509</v>
+        <v>276.3652989680743</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>306.9275772172747</v>
+        <v>306.9711598835637</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>304.345693</v>
+        <v>304.388985</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>296.76216</v>
+        <v>296.801882</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>289.178627</v>
+        <v>289.214779</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>281.595094</v>
+        <v>281.627676</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>274.011561</v>
+        <v>274.040574</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>305.636635</v>
+        <v>305.680072</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>298.020935</v>
+        <v>298.060788</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>290.405235</v>
+        <v>290.441504</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>282.789535</v>
+        <v>282.82222</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>275.173835</v>
+        <v>275.202936</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>306.927577</v>
+        <v>306.97116</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>299.27971</v>
+        <v>299.319695</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>291.631843</v>
+        <v>291.668229</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>283.983976</v>
+        <v>284.016764</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>276.336109</v>
+        <v>276.365299</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>308.218519</v>
+        <v>308.262248</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>300.538485</v>
+        <v>300.578601</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>292.858451</v>
+        <v>292.894955</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>285.178417</v>
+        <v>285.211308</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>277.498383</v>
+        <v>277.527662</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>309.509461</v>
+        <v>309.553335</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>301.79726</v>
+        <v>301.837507</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>294.085059</v>
+        <v>294.12168</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>286.372858</v>
+        <v>286.405852</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>278.660656</v>
+        <v>278.690024</v>
       </c>
     </row>
   </sheetData>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -25865,13 +25865,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5.163504</v>
+        <v>5.161227</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>3.924631</v>
+        <v>3.923962</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.041115</v>
+        <v>0.041134</v>
       </c>
     </row>
     <row r="3">
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.331365</v>
+        <v>8.32769</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.419058</v>
+        <v>4.417016</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.11998</v>
+        <v>0.120033</v>
       </c>
     </row>
     <row r="4">
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>23.132614</v>
+        <v>23.122411</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>7.888371</v>
+        <v>7.887022</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.004323</v>
+        <v>0.004325</v>
       </c>
     </row>
     <row r="8">
@@ -26109,10 +26109,10 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1294.032915</v>
+        <v>1293.462165</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>11.932453</v>
+        <v>11.929121</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>1.5e-05</v>
@@ -26150,10 +26150,10 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>27.15651</v>
+        <v>27.144532</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>14.400412</v>
+        <v>14.39559</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0</v>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.727337</v>
+        <v>10.725411</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -30127,7 +30127,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2545.502686</v>
+        <v>2545.921836</v>
       </c>
     </row>
     <row r="102">
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>104.4333447100331</v>
+        <v>104.4794267154209</v>
       </c>
     </row>
     <row r="118">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2537.905933600475</v>
+        <v>2538.667859835969</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3627.509648552048</v>
+        <v>3628.450992380046</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30413,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3596.514155</v>
+        <v>3597.447298</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3326.37564</v>
+        <v>3327.264301</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3056.237126</v>
+        <v>3057.081305</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2786.098612</v>
+        <v>2786.898309</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2515.960097</v>
+        <v>2516.715313</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30433,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3612.011902</v>
+        <v>3612.949145</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3340.74218</v>
+        <v>3341.634755</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3069.472459</v>
+        <v>3070.320366</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2798.202737</v>
+        <v>2799.005976</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2526.933015</v>
+        <v>2527.691586</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30453,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3627.509649</v>
+        <v>3628.450992</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3355.10872</v>
+        <v>3356.005209</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3082.707791</v>
+        <v>3083.559426</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2810.306862</v>
+        <v>2811.113643</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2537.905934</v>
+        <v>2538.66786</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30473,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3643.007395</v>
+        <v>3643.95284</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3369.47526</v>
+        <v>3370.375663</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3095.943124</v>
+        <v>3096.798487</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2822.410988</v>
+        <v>2823.22131</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2548.878852</v>
+        <v>2549.644133</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30493,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3658.505142</v>
+        <v>3659.454687</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3383.841799</v>
+        <v>3384.746117</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3109.178456</v>
+        <v>3110.037547</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2834.515113</v>
+        <v>2835.328977</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2559.85177</v>
+        <v>2560.620407</v>
       </c>
     </row>
   </sheetData>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4962807855630081</v>
+        <v>0.4964997732234882</v>
       </c>
     </row>
     <row r="92">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2386.78259</v>
+        <v>2387.349418</v>
       </c>
     </row>
     <row r="102">
@@ -34454,7 +34454,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>295.1516523804149</v>
+        <v>295.2818902854917</v>
       </c>
     </row>
     <row r="118">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1872.995070885319</v>
+        <v>1873.557662328628</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2322.124224482865</v>
+        <v>2322.794708178907</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2306.27705</v>
+        <v>2306.943876</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2191.362958</v>
+        <v>2192.001441</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2076.448866</v>
+        <v>2077.059006</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1961.534773</v>
+        <v>1962.116571</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1846.620681</v>
+        <v>1847.174136</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2317.855348</v>
+        <v>2318.525616</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2202.429802</v>
+        <v>2203.071606</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2087.004257</v>
+        <v>2087.617596</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1971.578711</v>
+        <v>1972.163586</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1856.153165</v>
+        <v>1856.709576</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2329.433646</v>
+        <v>2330.107355</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2213.496647</v>
+        <v>2214.14177</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2097.559648</v>
+        <v>2098.176185</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1981.622649</v>
+        <v>1982.2106</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1865.685649</v>
+        <v>1866.245015</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2341.011944</v>
+        <v>2341.689094</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2224.563491</v>
+        <v>2225.211935</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2108.115039</v>
+        <v>2108.734775</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1991.666586</v>
+        <v>1992.257615</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1875.218134</v>
+        <v>1875.780455</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2352.590242</v>
+        <v>2353.270834</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2235.630336</v>
+        <v>2236.282099</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2118.67043</v>
+        <v>2119.293364</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2001.710524</v>
+        <v>2002.30463</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1884.750618</v>
+        <v>1885.315895</v>
       </c>
     </row>
   </sheetData>
@@ -38281,7 +38281,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -46653,7 +46653,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.799573</v>
+        <v>1.79878</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>29.71102080950602</v>
+        <v>29.70491363108861</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>35.81275947975273</v>
+        <v>35.80665230133532</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.888314</v>
+        <v>1.888671</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47198,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>35.513344</v>
+        <v>35.507288</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>34.000663</v>
+        <v>33.994607</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>32.487982</v>
+        <v>32.481926</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>30.975301</v>
+        <v>30.969245</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>29.46262</v>
+        <v>29.456563</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47218,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>35.663052</v>
+        <v>35.65697</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>34.143994</v>
+        <v>34.137912</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>32.624936</v>
+        <v>32.618854</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>31.105878</v>
+        <v>31.099796</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>29.58682</v>
+        <v>29.580739</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47238,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>35.812759</v>
+        <v>35.806652</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>34.287325</v>
+        <v>34.281218</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>32.76189</v>
+        <v>32.755783</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>31.236455</v>
+        <v>31.230348</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>29.711021</v>
+        <v>29.704914</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47258,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>35.962467</v>
+        <v>35.956334</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>34.430656</v>
+        <v>34.424523</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>32.898844</v>
+        <v>32.892712</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>31.367033</v>
+        <v>31.3609</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>29.835221</v>
+        <v>29.829089</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47278,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>36.112175</v>
+        <v>36.106017</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>34.573987</v>
+        <v>34.567828</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>33.035798</v>
+        <v>33.02964</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>31.49761</v>
+        <v>31.491452</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>29.959422</v>
+        <v>29.953264</v>
       </c>
     </row>
   </sheetData>
@@ -50891,7 +50891,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="79">
@@ -51024,7 +51024,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.342809460542839</v>
+        <v>1.343401985401325</v>
       </c>
     </row>
     <row r="92">
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>961.794291</v>
+        <v>931.4132090000001</v>
       </c>
     </row>
     <row r="102">
@@ -51143,7 +51143,7 @@
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>5.338782673485778</v>
+        <v>5.341138451830394</v>
       </c>
     </row>
     <row r="106">
@@ -51174,7 +51174,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>963.9021906533591</v>
+        <v>933.3727091864765</v>
       </c>
     </row>
     <row r="109">
@@ -51204,7 +51204,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>1282.024052880507</v>
+        <v>1241.316674891721</v>
       </c>
     </row>
     <row r="112">
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>1.284058</v>
+        <v>1.325942</v>
       </c>
     </row>
     <row r="116">
@@ -51387,19 +51387,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>1273.202876</v>
+        <v>1232.843669</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>1193.294023</v>
+        <v>1155.457118</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1113.385169</v>
+        <v>1078.070568</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>1033.476315</v>
+        <v>1000.684017</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>953.567462</v>
+        <v>923.297467</v>
       </c>
     </row>
     <row r="130">
@@ -51407,19 +51407,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>1278.698844</v>
+        <v>1238.16603</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>1198.446492</v>
+        <v>1160.446832</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>1118.19414</v>
+        <v>1082.727634</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>1037.941789</v>
+        <v>1005.008436</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>957.689437</v>
+        <v>927.289238</v>
       </c>
     </row>
     <row r="131">
@@ -51427,19 +51427,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>1284.194811</v>
+        <v>1243.488391</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>1203.598961</v>
+        <v>1165.436545</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>1123.003112</v>
+        <v>1087.3847</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1042.407262</v>
+        <v>1009.332854</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>961.811413</v>
+        <v>931.281009</v>
       </c>
     </row>
     <row r="132">
@@ -51447,19 +51447,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>1289.690778</v>
+        <v>1248.810752</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>1208.751431</v>
+        <v>1170.426259</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>1127.812083</v>
+        <v>1092.041766</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1046.872736</v>
+        <v>1013.657273</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>965.933388</v>
+        <v>935.272779</v>
       </c>
     </row>
     <row r="133">
@@ -51467,19 +51467,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>1295.186746</v>
+        <v>1254.133113</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>1213.9039</v>
+        <v>1175.415973</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>1132.621055</v>
+        <v>1096.698832</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1051.338209</v>
+        <v>1017.981691</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>970.0553640000001</v>
+        <v>939.26455</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T19:34:52+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T23:33:14+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17299,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19096,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>0.001343431953985155</v>
+        <v>0.001357048829437667</v>
       </c>
       <c r="G46" s="15" t="n">
         <v>0.001070995536956725</v>
@@ -20724,7 +20724,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.3854199733698861</v>
+        <v>0.3893265469471483</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>-0.05479193513931103</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>520</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77">
@@ -21001,7 +21001,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.675937415769593</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847498</v>
+        <v>0.826827</v>
       </c>
     </row>
     <row r="104">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>276.3652989680743</v>
+        <v>277.1788908424364</v>
       </c>
     </row>
     <row r="121">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>306.9711598835637</v>
+        <v>308.1765701877188</v>
       </c>
     </row>
     <row r="124">
@@ -21368,19 +21368,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>304.388985</v>
+        <v>305.617023</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>296.801882</v>
+        <v>297.931965</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>289.214779</v>
+        <v>290.246908</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>281.627676</v>
+        <v>282.561851</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>274.040574</v>
+        <v>274.876793</v>
       </c>
     </row>
     <row r="133">
@@ -21388,19 +21388,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>305.680072</v>
+        <v>306.896796</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>298.060788</v>
+        <v>299.179558</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>290.441504</v>
+        <v>291.462319</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>282.82222</v>
+        <v>283.745081</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>275.202936</v>
+        <v>276.027842</v>
       </c>
     </row>
     <row r="134">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>306.97116</v>
+        <v>308.17657</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>299.319695</v>
+        <v>300.42715</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>291.668229</v>
+        <v>292.677731</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>284.016764</v>
+        <v>284.928311</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>276.365299</v>
+        <v>277.178891</v>
       </c>
     </row>
     <row r="135">
@@ -21428,19 +21428,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>308.262248</v>
+        <v>309.456344</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>300.578601</v>
+        <v>301.674743</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>292.894955</v>
+        <v>293.893142</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>285.211308</v>
+        <v>286.111541</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>277.527662</v>
+        <v>278.32994</v>
       </c>
     </row>
     <row r="136">
@@ -21448,19 +21448,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>309.553335</v>
+        <v>310.736118</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>301.837507</v>
+        <v>302.922335</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>294.12168</v>
+        <v>295.108553</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>286.405852</v>
+        <v>287.294771</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>278.690024</v>
+        <v>279.480988</v>
       </c>
     </row>
   </sheetData>
@@ -25906,13 +25906,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>8.32769</v>
+        <v>8.124575</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.417016</v>
+        <v>4.304131</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.120033</v>
+        <v>0.123034</v>
       </c>
     </row>
     <row r="4">
@@ -26270,7 +26270,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>10.725411</v>
+        <v>9.684742999999999</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -30537,7 +30537,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>2460</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="77">
@@ -34239,7 +34239,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.4964997732234882</v>
+        <v>0.5089122675540755</v>
       </c>
     </row>
     <row r="92">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>1873.557662328628</v>
+        <v>1874.669376185232</v>
       </c>
     </row>
     <row r="121">
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>2322.794708178907</v>
+        <v>2324.144995142849</v>
       </c>
     </row>
     <row r="124">
@@ -34606,19 +34606,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>2306.943876</v>
+        <v>2308.294163</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>2192.001441</v>
+        <v>2193.292085</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>2077.059006</v>
+        <v>2078.290006</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1962.116571</v>
+        <v>1963.287928</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>1847.174136</v>
+        <v>1848.28585</v>
       </c>
     </row>
     <row r="133">
@@ -34626,19 +34626,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>2318.525616</v>
+        <v>2319.875903</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>2203.071606</v>
+        <v>2204.362249</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>2087.617596</v>
+        <v>2088.848596</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1972.163586</v>
+        <v>1973.334943</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1856.709576</v>
+        <v>1857.821289</v>
       </c>
     </row>
     <row r="134">
@@ -34646,19 +34646,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>2330.107355</v>
+        <v>2331.457642</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>2214.14177</v>
+        <v>2215.432414</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>2098.176185</v>
+        <v>2099.407186</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>1982.2106</v>
+        <v>1983.381957</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>1866.245015</v>
+        <v>1867.356729</v>
       </c>
     </row>
     <row r="135">
@@ -34666,19 +34666,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>2341.689094</v>
+        <v>2343.039381</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2225.211935</v>
+        <v>2226.502578</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2108.734775</v>
+        <v>2109.965775</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>1992.257615</v>
+        <v>1993.428972</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1875.780455</v>
+        <v>1876.892169</v>
       </c>
     </row>
     <row r="136">
@@ -34686,19 +34686,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>2353.270834</v>
+        <v>2354.621121</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>2236.282099</v>
+        <v>2237.572743</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>2119.293364</v>
+        <v>2120.524365</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2002.30463</v>
+        <v>2003.475987</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>1885.315895</v>
+        <v>1886.427609</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T23:33:14+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-31T02:24:26+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -25886,11 +25886,11 @@
         </is>
       </c>
       <c r="C3" s="6">
-        <f>'ADRO'!$C$128</f>
+        <f>'ADRO'!$C$122</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>'ADRO'!$C$126</f>
+        <f>'ADRO'!$C$120</f>
         <v/>
       </c>
       <c r="E3" s="7">
@@ -25898,11 +25898,11 @@
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>'ADRO'!$C$127</f>
+        <f>'ADRO'!$C$121</f>
         <v/>
       </c>
       <c r="G3" s="7">
-        <f>'ADRO'!$C$116</f>
+        <f>'ADRO'!$C$110</f>
         <v/>
       </c>
       <c r="H3" s="9" t="n">
@@ -26030,7 +26030,7 @@
       </c>
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n">
-        <v>33.24141</v>
+        <v>30.78897</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>0</v>
@@ -26068,13 +26068,13 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>23.122411</v>
+        <v>32.08584</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>7.887022</v>
+        <v>9.54707</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.004325</v>
+        <v>0.003117</v>
       </c>
     </row>
     <row r="8">
@@ -30519,7 +30519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q136"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -30537,7 +30537,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -34166,7 +34166,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>4609.002</v>
+        <v>4485.423</v>
       </c>
     </row>
     <row r="85">
@@ -34320,13 +34320,13 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>2387.349418</v>
+        <v>2058.735749</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>P/E</t>
+          <t>P/BV</t>
         </is>
       </c>
     </row>
@@ -34337,7 +34337,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>4.069228</v>
+        <v>0.901424</v>
       </c>
     </row>
     <row r="104">
@@ -34347,13 +34347,13 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>447.69422</v>
+        <v>4485.423</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — P/E</t>
+          <t>Value per share (IDR) — P/BV</t>
         </is>
       </c>
       <c r="C105" s="23">
@@ -34364,341 +34364,293 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>P/BV</t>
+          <t>TARGET</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Target multiple (own five-year average)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n">
-        <v>0.901424</v>
+          <t>Weight: Sum of the parts</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Metric (LTM, or next-12m DPS for yield)</t>
-        </is>
-      </c>
-      <c r="C109" s="13" t="n">
-        <v>4609.002</v>
+          <t>Weight: P/BV</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — P/BV</t>
+          <t>Value today (weighted)</t>
         </is>
       </c>
       <c r="C110" s="23">
-        <f>MAX(0,$C$108*$C$109/$C$77*$C$85*$C$78)</f>
-        <v/>
+        <f>$C$100*$C$108+$C$105*$C$109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DPS expected in next 12 months (IDR)</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>295.2818902854917</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>TARGET</t>
-        </is>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Base-case 12-month value</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>MAX(0,$C$110*(1+$C$94)-$C$111)</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Weight: Sum of the parts</t>
+          <t>Bear probability</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Weight: P/E</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>0.25</v>
+          <t>Bear 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="n">
+        <v>1890.421979004725</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Weight: P/BV</t>
+          <t>Base probability</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Value today (weighted)</t>
-        </is>
-      </c>
-      <c r="C116" s="23">
-        <f>$C$100*$C$113+$C$105*$C$114+$C$110*$C$115</f>
-        <v/>
+          <t>Bull probability</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DPS expected in next 12 months (IDR)</t>
+          <t>Bull 12-month value (engine)</t>
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>295.2818902854917</v>
+        <v>2409.421204909924</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Base-case 12-month value</t>
+          <t>Probability-weighted 12-month value</t>
         </is>
       </c>
       <c r="C118" s="23">
-        <f>MAX(0,$C$116*(1+$C$94)-$C$117)</f>
+        <f>$C$113*$C$114+$C$115*$C$112+$C$116*$C$117</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bear probability</t>
+          <t>Liquidity discount (limits.yaml)</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bear 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>1874.669376185232</v>
+          <t>TARGET PRICE (IDR)</t>
+        </is>
+      </c>
+      <c r="C120" s="24">
+        <f>$C$118*(1-$C$119)</f>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Base probability</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>0.5</v>
+          <t>Expected 12-month total return</t>
+        </is>
+      </c>
+      <c r="C121" s="25">
+        <f>($C$120+$C$111)/$C$76-1</f>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bull probability</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Bull 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n">
-        <v>2324.144995142849</v>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C122" s="26">
+        <f>IF($C$121&gt;=0.25,"BUY",IF($C$121&gt;=0.1,"ADD",IF($C$121&lt;=-0.25,"SELL",IF($C$121&lt;=-0.1,"REDUCE","HOLD"))))</f>
+        <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Probability-weighted 12-month value</t>
-        </is>
-      </c>
-      <c r="C124" s="23">
-        <f>$C$119*$C$120+$C$121*$C$118+$C$122*$C$123</f>
-        <v/>
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Liquidity discount (limits.yaml)</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F125" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="G125" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H125" s="1" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>TARGET PRICE (IDR)</t>
-        </is>
-      </c>
-      <c r="C126" s="24">
-        <f>$C$124*(1-$C$125)</f>
-        <v/>
+      <c r="C126" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D126" s="23" t="n">
+        <v>2392.818379</v>
+      </c>
+      <c r="E126" s="23" t="n">
+        <v>2260.588669</v>
+      </c>
+      <c r="F126" s="23" t="n">
+        <v>2128.35896</v>
+      </c>
+      <c r="G126" s="23" t="n">
+        <v>1996.12925</v>
+      </c>
+      <c r="H126" s="23" t="n">
+        <v>1863.899541</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Expected 12-month total return</t>
-        </is>
-      </c>
-      <c r="C127" s="25">
-        <f>($C$126+$C$117)/$C$76-1</f>
-        <v/>
+      <c r="C127" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D127" s="23" t="n">
+        <v>2404.776115</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <v>2271.958196</v>
+      </c>
+      <c r="F127" s="23" t="n">
+        <v>2139.140276</v>
+      </c>
+      <c r="G127" s="23" t="n">
+        <v>2006.322356</v>
+      </c>
+      <c r="H127" s="23" t="n">
+        <v>1873.504436</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="C128" s="26">
-        <f>IF($C$127&gt;=0.25,"BUY",IF($C$127&gt;=0.1,"ADD",IF($C$127&lt;=-0.25,"SELL",IF($C$127&lt;=-0.1,"REDUCE","HOLD"))))</f>
-        <v/>
+      <c r="C128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>2416.733852</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>2283.327722</v>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>2149.921592</v>
+      </c>
+      <c r="G128" s="23" t="n">
+        <v>2016.515462</v>
+      </c>
+      <c r="H128" s="23" t="n">
+        <v>1883.109332</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>2428.691588</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>2294.697248</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>2160.702908</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <v>2026.708568</v>
+      </c>
+      <c r="H129" s="23" t="n">
+        <v>1892.714228</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H131" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="C132" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D132" s="23" t="n">
-        <v>2308.294163</v>
-      </c>
-      <c r="E132" s="23" t="n">
-        <v>2193.292085</v>
-      </c>
-      <c r="F132" s="23" t="n">
-        <v>2078.290006</v>
-      </c>
-      <c r="G132" s="23" t="n">
-        <v>1963.287928</v>
-      </c>
-      <c r="H132" s="23" t="n">
-        <v>1848.28585</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="C133" s="1" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D133" s="23" t="n">
-        <v>2319.875903</v>
-      </c>
-      <c r="E133" s="23" t="n">
-        <v>2204.362249</v>
-      </c>
-      <c r="F133" s="23" t="n">
-        <v>2088.848596</v>
-      </c>
-      <c r="G133" s="23" t="n">
-        <v>1973.334943</v>
-      </c>
-      <c r="H133" s="23" t="n">
-        <v>1857.821289</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="C134" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="23" t="n">
-        <v>2331.457642</v>
-      </c>
-      <c r="E134" s="23" t="n">
-        <v>2215.432414</v>
-      </c>
-      <c r="F134" s="23" t="n">
-        <v>2099.407186</v>
-      </c>
-      <c r="G134" s="23" t="n">
-        <v>1983.381957</v>
-      </c>
-      <c r="H134" s="23" t="n">
-        <v>1867.356729</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="C135" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D135" s="23" t="n">
-        <v>2343.039381</v>
-      </c>
-      <c r="E135" s="23" t="n">
-        <v>2226.502578</v>
-      </c>
-      <c r="F135" s="23" t="n">
-        <v>2109.965775</v>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>1993.428972</v>
-      </c>
-      <c r="H135" s="23" t="n">
-        <v>1876.892169</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="C136" s="1" t="n">
+      <c r="C130" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="D136" s="23" t="n">
-        <v>2354.621121</v>
-      </c>
-      <c r="E136" s="23" t="n">
-        <v>2237.572743</v>
-      </c>
-      <c r="F136" s="23" t="n">
-        <v>2120.524365</v>
-      </c>
-      <c r="G136" s="23" t="n">
-        <v>2003.475987</v>
-      </c>
-      <c r="H136" s="23" t="n">
-        <v>1886.427609</v>
+      <c r="D130" s="23" t="n">
+        <v>2440.649325</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>2306.066775</v>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>2171.484224</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <v>2036.901674</v>
+      </c>
+      <c r="H130" s="23" t="n">
+        <v>1902.319124</v>
       </c>
     </row>
   </sheetData>
@@ -43092,7 +43044,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -46633,7 +46585,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77">
@@ -46787,7 +46739,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>1.651906620794722</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -46885,7 +46837,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.79878</v>
+        <v>1.788444</v>
       </c>
     </row>
     <row r="104">
@@ -46985,7 +46937,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>29.70491363108861</v>
+        <v>30.03030087720204</v>
       </c>
     </row>
     <row r="115">
@@ -47015,7 +46967,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>35.80665230133532</v>
+        <v>36.21543623575474</v>
       </c>
     </row>
     <row r="118">
@@ -47057,7 +47009,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.888671</v>
+        <v>1.522091</v>
       </c>
     </row>
     <row r="122">
@@ -47198,19 +47150,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>35.507288</v>
+        <v>35.916737</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>33.994607</v>
+        <v>34.383207</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>32.481926</v>
+        <v>32.849676</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>30.969245</v>
+        <v>31.316146</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>29.456563</v>
+        <v>29.782616</v>
       </c>
     </row>
     <row r="136">
@@ -47218,19 +47170,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>35.65697</v>
+        <v>36.066087</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>34.137912</v>
+        <v>34.526179</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>32.618854</v>
+        <v>32.986272</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>31.099796</v>
+        <v>31.446365</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>29.580739</v>
+        <v>29.906458</v>
       </c>
     </row>
     <row r="137">
@@ -47238,19 +47190,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>35.806652</v>
+        <v>36.215436</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>34.281218</v>
+        <v>34.669152</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>32.755783</v>
+        <v>33.122869</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>31.230348</v>
+        <v>31.576585</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>29.704914</v>
+        <v>30.030301</v>
       </c>
     </row>
     <row r="138">
@@ -47258,19 +47210,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>35.956334</v>
+        <v>36.364786</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>34.424523</v>
+        <v>34.812125</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>32.892712</v>
+        <v>33.259465</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>31.3609</v>
+        <v>31.706804</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>29.829089</v>
+        <v>30.154144</v>
       </c>
     </row>
     <row r="139">
@@ -47278,19 +47230,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>36.106017</v>
+        <v>36.514136</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>34.567828</v>
+        <v>34.955098</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>33.02964</v>
+        <v>33.396061</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>31.491452</v>
+        <v>31.837024</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>29.953264</v>
+        <v>30.277986</v>
       </c>
     </row>
   </sheetData>
@@ -47322,7 +47274,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -47454,7 +47406,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.490285</v>
+        <v>0.518435</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0.1</v>
@@ -47496,34 +47448,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.181466</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.213614</v>
+        <v>0.150493</v>
       </c>
     </row>
     <row r="13">
@@ -51105,7 +51057,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>931.4132090000001</v>
+        <v>418.221227</v>
       </c>
     </row>
     <row r="102">
@@ -51143,7 +51095,7 @@
         </is>
       </c>
       <c r="C105" s="15" t="n">
-        <v>5.341138451830394</v>
+        <v>3.849049951708628</v>
       </c>
     </row>
     <row r="106">
@@ -51174,7 +51126,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>933.3727091864765</v>
+        <v>418.8081705935782</v>
       </c>
     </row>
     <row r="109">
@@ -51204,7 +51156,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>1241.316674891721</v>
+        <v>554.7206923963233</v>
       </c>
     </row>
     <row r="112">
@@ -51246,7 +51198,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>1.325942</v>
+        <v>2.952983</v>
       </c>
     </row>
     <row r="116">
@@ -51387,19 +51339,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>1232.843669</v>
+        <v>552.118124</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>1155.457118</v>
+        <v>517.370175</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1078.070568</v>
+        <v>482.622227</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>1000.684017</v>
+        <v>447.874279</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>923.297467</v>
+        <v>413.12633</v>
       </c>
     </row>
     <row r="130">
@@ -51407,19 +51359,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>1238.16603</v>
+        <v>554.507959</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>1160.446832</v>
+        <v>519.610646</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>1082.727634</v>
+        <v>484.713333</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>1005.008436</v>
+        <v>449.81602</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>927.289238</v>
+        <v>414.918707</v>
       </c>
     </row>
     <row r="131">
@@ -51427,19 +51379,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>1243.488391</v>
+        <v>556.897795</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>1165.436545</v>
+        <v>521.851117</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>1087.3847</v>
+        <v>486.804439</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1009.332854</v>
+        <v>451.757761</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>931.281009</v>
+        <v>416.711084</v>
       </c>
     </row>
     <row r="132">
@@ -51447,19 +51399,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>1248.810752</v>
+        <v>559.28763</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>1170.426259</v>
+        <v>524.091588</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>1092.041766</v>
+        <v>488.895545</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>1013.657273</v>
+        <v>453.699503</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>935.272779</v>
+        <v>418.50346</v>
       </c>
     </row>
     <row r="133">
@@ -51467,19 +51419,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>1254.133113</v>
+        <v>561.677466</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>1175.415973</v>
+        <v>526.332059</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>1096.698832</v>
+        <v>490.986651</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>1017.981691</v>
+        <v>455.641244</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>939.26455</v>
+        <v>420.295837</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-31T02:24:26+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-31T05:02:47+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>0.847498</v>
+        <v>0.826827</v>
       </c>
     </row>
     <row r="104">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>38.90443922301376</v>
+        <v>38.66082801341696</v>
       </c>
     </row>
     <row r="115">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>53.22454916970256</v>
+        <v>52.98025475836653</v>
       </c>
     </row>
     <row r="118">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>9.410624</v>
+        <v>9.455582</v>
       </c>
     </row>
     <row r="122">
@@ -4760,19 +4760,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>51.066542</v>
+        <v>50.821718</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>48.432583</v>
+        <v>48.18916</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>45.798624</v>
+        <v>45.556602</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>43.164666</v>
+        <v>42.924043</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>40.530707</v>
+        <v>40.291485</v>
       </c>
     </row>
     <row r="136">
@@ -4780,19 +4780,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>51.292846</v>
+        <v>51.047057</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>48.647216</v>
+        <v>48.402828</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>46.001586</v>
+        <v>45.758599</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>43.355957</v>
+        <v>43.114369</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>40.710327</v>
+        <v>40.47014</v>
       </c>
     </row>
     <row r="137">
@@ -4800,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>51.519151</v>
+        <v>51.272397</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>48.86185</v>
+        <v>48.616496</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>46.204549</v>
+        <v>45.960596</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>43.547247</v>
+        <v>43.304695</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>40.889946</v>
+        <v>40.648795</v>
       </c>
     </row>
     <row r="138">
@@ -4820,19 +4820,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>51.745455</v>
+        <v>51.497736</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>49.076483</v>
+        <v>48.830165</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>46.407511</v>
+        <v>46.162593</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>43.738538</v>
+        <v>43.495021</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>41.069566</v>
+        <v>40.827449</v>
       </c>
     </row>
     <row r="139">
@@ -4840,19 +4840,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>51.97176</v>
+        <v>51.723076</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>49.291116</v>
+        <v>49.043833</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>46.610473</v>
+        <v>46.36459</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>43.929829</v>
+        <v>43.685347</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>41.249186</v>
+        <v>41.006104</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4884,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>215.983721</v>
+        <v>215.995221</v>
       </c>
     </row>
     <row r="102">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>208.3971453533571</v>
+        <v>208.2971579634125</v>
       </c>
     </row>
     <row r="109">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>277.8628604711428</v>
+        <v>277.7295439512166</v>
       </c>
     </row>
     <row r="112">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="C115" s="18" t="n">
-        <v>3.147719</v>
+        <v>3.147552</v>
       </c>
     </row>
     <row r="116">
@@ -8941,19 +8941,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>275.394475</v>
+        <v>275.261027</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>258.18232</v>
+        <v>258.057213</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>240.970166</v>
+        <v>240.853399</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>223.758011</v>
+        <v>223.649585</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>206.545856</v>
+        <v>206.44577</v>
       </c>
     </row>
     <row r="130">
@@ -8961,19 +8961,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>276.628668</v>
+        <v>276.495286</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>259.339376</v>
+        <v>259.21433</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>242.050084</v>
+        <v>241.933375</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>224.760793</v>
+        <v>224.65242</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>207.471501</v>
+        <v>207.371464</v>
       </c>
     </row>
     <row r="131">
@@ -8981,19 +8981,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>277.86286</v>
+        <v>277.729544</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>260.496432</v>
+        <v>260.371447</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>243.130003</v>
+        <v>243.013351</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>225.763574</v>
+        <v>225.655254</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>208.397145</v>
+        <v>208.297158</v>
       </c>
     </row>
     <row r="132">
@@ -9001,19 +9001,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>279.097053</v>
+        <v>278.963802</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>261.653487</v>
+        <v>261.528565</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>244.209922</v>
+        <v>244.093327</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>226.766356</v>
+        <v>226.658089</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>209.32279</v>
+        <v>209.222852</v>
       </c>
     </row>
     <row r="133">
@@ -9021,19 +9021,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>280.331246</v>
+        <v>280.198061</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>262.810543</v>
+        <v>262.685682</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>245.28984</v>
+        <v>245.173303</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>227.769137</v>
+        <v>227.660924</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>210.248434</v>
+        <v>210.148546</v>
       </c>
     </row>
   </sheetData>
@@ -9065,7 +9065,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -13153,7 +13153,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q136"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17299,7 +17299,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.015</v>
+        <v>-0.0664</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0.06</v>
@@ -17473,34 +17473,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.163</v>
+        <v>0.18</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.163</v>
+        <v>0.18</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="28">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>167.169365</v>
+        <v>145.588006</v>
       </c>
     </row>
     <row r="85">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>150.179112</v>
+        <v>396.089019</v>
       </c>
     </row>
     <row r="102">
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>167.169365</v>
+        <v>145.588006</v>
       </c>
     </row>
     <row r="105">
@@ -21126,341 +21126,293 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
+          <t>TARGET</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Target multiple (peer median)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n">
-        <v>14.296665</v>
+          <t>Weight: Sum of the parts</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0.666667</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Metric (LTM, or next-12m DPS for yield)</t>
-        </is>
-      </c>
-      <c r="C109" s="13" t="n">
-        <v>43.168323</v>
+          <t>Weight: P/BV</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0.333333</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — EV/EBITDA</t>
+          <t>Value today (weighted)</t>
         </is>
       </c>
       <c r="C110" s="23">
-        <f>MAX(0,($C$108*$C$109-($C$79-$C$80)-$C$81+$C$82+$C$83)/$C$77*$C$85*$C$78)</f>
-        <v/>
+        <f>$C$100*$C$108+$C$105*$C$109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DPS expected in next 12 months (IDR)</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>TARGET</t>
-        </is>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Base-case 12-month value</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>MAX(0,$C$110*(1+$C$94)-$C$111)</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Weight: Sum of the parts</t>
+          <t>Bear probability</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Weight: P/BV</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>0.3</v>
+          <t>Bear 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="n">
+        <v>366.4327653700028</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Weight: EV/EBITDA</t>
+          <t>Base probability</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Value today (weighted)</t>
-        </is>
-      </c>
-      <c r="C116" s="23">
-        <f>$C$100*$C$113+$C$105*$C$114+$C$110*$C$115</f>
-        <v/>
+          <t>Bull probability</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DPS expected in next 12 months (IDR)</t>
+          <t>Bull 12-month value (engine)</t>
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>0</v>
+        <v>479.9243028711895</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Base-case 12-month value</t>
+          <t>Probability-weighted 12-month value</t>
         </is>
       </c>
       <c r="C118" s="23">
-        <f>MAX(0,$C$116*(1+$C$94)-$C$117)</f>
+        <f>$C$113*$C$114+$C$115*$C$112+$C$116*$C$117</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bear probability</t>
+          <t>Liquidity discount (limits.yaml)</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bear 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>277.1788908424364</v>
+          <t>TARGET PRICE (IDR)</t>
+        </is>
+      </c>
+      <c r="C120" s="24">
+        <f>$C$118*(1-$C$119)</f>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Base probability</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>0.5</v>
+          <t>Expected 12-month total return</t>
+        </is>
+      </c>
+      <c r="C121" s="25">
+        <f>($C$120+$C$111)/$C$76-1</f>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bull probability</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Bull 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n">
-        <v>308.1765701877188</v>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C122" s="26">
+        <f>IF($C$121&gt;=0.25,"BUY",IF($C$121&gt;=0.1,"ADD",IF($C$121&lt;=-0.25,"SELL",IF($C$121&lt;=-0.1,"REDUCE","HOLD"))))</f>
+        <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Probability-weighted 12-month value</t>
-        </is>
-      </c>
-      <c r="C124" s="23">
-        <f>$C$119*$C$120+$C$121*$C$118+$C$122*$C$123</f>
-        <v/>
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Liquidity discount (limits.yaml)</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>0</v>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H125" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>TARGET PRICE (IDR)</t>
-        </is>
-      </c>
-      <c r="C126" s="24">
-        <f>$C$124*(1-$C$125)</f>
-        <v/>
+      <c r="C126" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D126" s="23" t="n">
+        <v>475.936325</v>
+      </c>
+      <c r="E126" s="23" t="n">
+        <v>447.799208</v>
+      </c>
+      <c r="F126" s="23" t="n">
+        <v>419.66209</v>
+      </c>
+      <c r="G126" s="23" t="n">
+        <v>391.524973</v>
+      </c>
+      <c r="H126" s="23" t="n">
+        <v>363.387856</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Expected 12-month total return</t>
-        </is>
-      </c>
-      <c r="C127" s="25">
-        <f>($C$126+$C$117)/$C$76-1</f>
-        <v/>
+      <c r="C127" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D127" s="23" t="n">
+        <v>477.930314</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <v>449.675313</v>
+      </c>
+      <c r="F127" s="23" t="n">
+        <v>421.420312</v>
+      </c>
+      <c r="G127" s="23" t="n">
+        <v>393.165312</v>
+      </c>
+      <c r="H127" s="23" t="n">
+        <v>364.910311</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="C128" s="26">
-        <f>IF($C$127&gt;=0.25,"BUY",IF($C$127&gt;=0.1,"ADD",IF($C$127&lt;=-0.25,"SELL",IF($C$127&lt;=-0.1,"REDUCE","HOLD"))))</f>
-        <v/>
+      <c r="C128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>479.924303</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>451.551418</v>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>423.178534</v>
+      </c>
+      <c r="G128" s="23" t="n">
+        <v>394.80565</v>
+      </c>
+      <c r="H128" s="23" t="n">
+        <v>366.432765</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>481.918292</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>453.427524</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>424.936756</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <v>396.445988</v>
+      </c>
+      <c r="H129" s="23" t="n">
+        <v>367.95522</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>12-month value vs holding-company discount and cost of equity (engine values)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>rows: Cost of equity (+/- pp) · columns: Holdco discount (+/- pp)</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H131" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="C132" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D132" s="23" t="n">
-        <v>305.617023</v>
-      </c>
-      <c r="E132" s="23" t="n">
-        <v>297.931965</v>
-      </c>
-      <c r="F132" s="23" t="n">
-        <v>290.246908</v>
-      </c>
-      <c r="G132" s="23" t="n">
-        <v>282.561851</v>
-      </c>
-      <c r="H132" s="23" t="n">
-        <v>274.876793</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="C133" s="1" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D133" s="23" t="n">
-        <v>306.896796</v>
-      </c>
-      <c r="E133" s="23" t="n">
-        <v>299.179558</v>
-      </c>
-      <c r="F133" s="23" t="n">
-        <v>291.462319</v>
-      </c>
-      <c r="G133" s="23" t="n">
-        <v>283.745081</v>
-      </c>
-      <c r="H133" s="23" t="n">
-        <v>276.027842</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="C134" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="23" t="n">
-        <v>308.17657</v>
-      </c>
-      <c r="E134" s="23" t="n">
-        <v>300.42715</v>
-      </c>
-      <c r="F134" s="23" t="n">
-        <v>292.677731</v>
-      </c>
-      <c r="G134" s="23" t="n">
-        <v>284.928311</v>
-      </c>
-      <c r="H134" s="23" t="n">
-        <v>277.178891</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="C135" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D135" s="23" t="n">
-        <v>309.456344</v>
-      </c>
-      <c r="E135" s="23" t="n">
-        <v>301.674743</v>
-      </c>
-      <c r="F135" s="23" t="n">
-        <v>293.893142</v>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>286.111541</v>
-      </c>
-      <c r="H135" s="23" t="n">
-        <v>278.32994</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="C136" s="1" t="n">
+      <c r="C130" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="D136" s="23" t="n">
-        <v>310.736118</v>
-      </c>
-      <c r="E136" s="23" t="n">
-        <v>302.922335</v>
-      </c>
-      <c r="F136" s="23" t="n">
-        <v>295.108553</v>
-      </c>
-      <c r="G136" s="23" t="n">
-        <v>287.294771</v>
-      </c>
-      <c r="H136" s="23" t="n">
-        <v>279.480988</v>
+      <c r="D130" s="23" t="n">
+        <v>483.912281</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>455.303629</v>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>426.694978</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <v>398.086326</v>
+      </c>
+      <c r="H130" s="23" t="n">
+        <v>369.477674</v>
       </c>
     </row>
   </sheetData>
@@ -21492,7 +21444,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -25656,7 +25608,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.04989</v>
+        <v>0.04929</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -25680,7 +25632,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25652,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25672,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -26030,7 +25982,7 @@
       </c>
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n">
-        <v>30.78897</v>
+        <v>22.909769</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>0</v>
@@ -26249,11 +26201,11 @@
         </is>
       </c>
       <c r="C12" s="6">
-        <f>'TOBA'!$C$128</f>
+        <f>'TOBA'!$C$122</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>'TOBA'!$C$126</f>
+        <f>'TOBA'!$C$120</f>
         <v/>
       </c>
       <c r="E12" s="7">
@@ -26261,16 +26213,16 @@
         <v/>
       </c>
       <c r="F12" s="8">
-        <f>'TOBA'!$C$127</f>
+        <f>'TOBA'!$C$121</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>'TOBA'!$C$116</f>
+        <f>'TOBA'!$C$110</f>
         <v/>
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>9.684742999999999</v>
+        <v>9.343093</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
@@ -26344,7 +26296,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -30292,7 +30244,7 @@
         </is>
       </c>
       <c r="C120" s="15" t="n">
-        <v>2538.667859835969</v>
+        <v>2537.350706996673</v>
       </c>
     </row>
     <row r="121">
@@ -30322,7 +30274,7 @@
         </is>
       </c>
       <c r="C123" s="15" t="n">
-        <v>3628.450992380046</v>
+        <v>3626.590770694548</v>
       </c>
     </row>
     <row r="124">
@@ -30413,19 +30365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3597.447298</v>
+        <v>3595.587076</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>3327.264301</v>
+        <v>3325.539847</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>3057.081305</v>
+        <v>3055.492618</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>2786.898309</v>
+        <v>2785.445389</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>2516.715313</v>
+        <v>2515.39816</v>
       </c>
     </row>
     <row r="133">
@@ -30433,19 +30385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>3612.949145</v>
+        <v>3611.088923</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3341.634755</v>
+        <v>3339.910301</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3070.320366</v>
+        <v>3068.731678</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>2799.005976</v>
+        <v>2797.553056</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>2527.691586</v>
+        <v>2526.374433</v>
       </c>
     </row>
     <row r="134">
@@ -30453,19 +30405,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>3628.450992</v>
+        <v>3626.590771</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>3356.005209</v>
+        <v>3354.280755</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>3083.559426</v>
+        <v>3081.970739</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>2811.113643</v>
+        <v>2809.660723</v>
       </c>
       <c r="H134" s="23" t="n">
-        <v>2538.66786</v>
+        <v>2537.350707</v>
       </c>
     </row>
     <row r="135">
@@ -30473,19 +30425,19 @@
         <v>0.005</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3643.95284</v>
+        <v>3642.092618</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3370.375663</v>
+        <v>3368.651209</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>3096.798487</v>
+        <v>3095.209799</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2823.22131</v>
+        <v>2821.76839</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>2549.644133</v>
+        <v>2548.326981</v>
       </c>
     </row>
     <row r="136">
@@ -30493,19 +30445,19 @@
         <v>0.01</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3659.454687</v>
+        <v>3657.594465</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3384.746117</v>
+        <v>3383.021663</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>3110.037547</v>
+        <v>3108.44886</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>2835.328977</v>
+        <v>2833.876057</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>2560.620407</v>
+        <v>2559.303254</v>
       </c>
     </row>
   </sheetData>
@@ -34437,7 +34389,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>1890.421979004725</v>
+        <v>1889.26939151775</v>
       </c>
     </row>
     <row r="115">
@@ -34467,7 +34419,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>2409.421204909924</v>
+        <v>2407.98627652028</v>
       </c>
     </row>
     <row r="118">
@@ -34558,19 +34510,19 @@
         <v>-0.01</v>
       </c>
       <c r="D126" s="23" t="n">
-        <v>2392.818379</v>
+        <v>2391.38345</v>
       </c>
       <c r="E126" s="23" t="n">
-        <v>2260.588669</v>
+        <v>2259.224326</v>
       </c>
       <c r="F126" s="23" t="n">
-        <v>2128.35896</v>
+        <v>2127.065202</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>1996.12925</v>
+        <v>1994.906077</v>
       </c>
       <c r="H126" s="23" t="n">
-        <v>1863.899541</v>
+        <v>1862.746953</v>
       </c>
     </row>
     <row r="127">
@@ -34578,19 +34530,19 @@
         <v>-0.005</v>
       </c>
       <c r="D127" s="23" t="n">
-        <v>2404.776115</v>
+        <v>2403.341187</v>
       </c>
       <c r="E127" s="23" t="n">
-        <v>2271.958196</v>
+        <v>2270.593852</v>
       </c>
       <c r="F127" s="23" t="n">
-        <v>2139.140276</v>
+        <v>2137.846518</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>2006.322356</v>
+        <v>2005.099183</v>
       </c>
       <c r="H127" s="23" t="n">
-        <v>1873.504436</v>
+        <v>1872.351849</v>
       </c>
     </row>
     <row r="128">
@@ -34598,19 +34550,19 @@
         <v>0</v>
       </c>
       <c r="D128" s="23" t="n">
-        <v>2416.733852</v>
+        <v>2415.298923</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>2283.327722</v>
+        <v>2281.963379</v>
       </c>
       <c r="F128" s="23" t="n">
-        <v>2149.921592</v>
+        <v>2148.627834</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>2016.515462</v>
+        <v>2015.292289</v>
       </c>
       <c r="H128" s="23" t="n">
-        <v>1883.109332</v>
+        <v>1881.956745</v>
       </c>
     </row>
     <row r="129">
@@ -34618,19 +34570,19 @@
         <v>0.005</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>2428.691588</v>
+        <v>2427.25666</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>2294.697248</v>
+        <v>2293.332905</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>2160.702908</v>
+        <v>2159.40915</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>2026.708568</v>
+        <v>2025.485395</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>1892.714228</v>
+        <v>1891.56164</v>
       </c>
     </row>
     <row r="130">
@@ -34638,19 +34590,19 @@
         <v>0.01</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>2440.649325</v>
+        <v>2439.214397</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>2306.066775</v>
+        <v>2304.702431</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>2171.484224</v>
+        <v>2170.190466</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>2036.901674</v>
+        <v>2035.678501</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>1902.319124</v>
+        <v>1901.166536</v>
       </c>
     </row>
   </sheetData>
@@ -34682,7 +34634,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-26</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -38858,7 +38810,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-27</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -43044,7 +42996,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: IDR bn; per-share in IDR unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -43176,7 +43128,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.38</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0.08</v>
@@ -43218,34 +43170,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.2743</v>
       </c>
     </row>
     <row r="13">
@@ -43260,34 +43212,34 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.142</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="14">
@@ -43302,34 +43254,34 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="15">
@@ -43344,34 +43296,34 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -43470,7 +43422,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.065</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="19">
@@ -43485,7 +43437,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.055</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
@@ -43500,34 +43452,34 @@
         </is>
       </c>
       <c r="H20" s="13" t="n">
-        <v>1000</v>
+        <v>-3410.9</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>635.5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>651.3874999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>667.6721874999998</v>
+        <v>0</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>684.3639921874997</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>701.4730919921872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -43542,7 +43494,7 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0</v>
+        <v>-114.492</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>0</v>
@@ -46655,7 +46607,7 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>4543</v>
+        <v>4371.992</v>
       </c>
     </row>
     <row r="84">
@@ -46665,7 +46617,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>8470.09</v>
+        <v>8303.696</v>
       </c>
     </row>
     <row r="85">
@@ -46820,7 +46772,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>19.767945</v>
+        <v>19.365323</v>
       </c>
     </row>
     <row r="102">
@@ -46837,7 +46789,7 @@
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.788444</v>
+        <v>0.787754</v>
       </c>
     </row>
     <row r="104">
@@ -46847,7 +46799,7 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>8470.09</v>
+        <v>8303.696</v>
       </c>
     </row>
     <row r="105">
@@ -46927,7 +46879,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="114">
@@ -46937,7 +46889,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>30.03030087720204</v>
+        <v>24.20086183397915</v>
       </c>
     </row>
     <row r="115">
@@ -46947,7 +46899,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
@@ -46957,7 +46909,7 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="117">
@@ -46967,7 +46919,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>36.21543623575474</v>
+        <v>25.41269390002948</v>
       </c>
     </row>
     <row r="118">
@@ -47009,7 +46961,7 @@
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>1.522091</v>
+        <v>2.003885</v>
       </c>
     </row>
     <row r="122">
@@ -47150,19 +47102,19 @@
         <v>-0.01</v>
       </c>
       <c r="D135" s="23" t="n">
-        <v>35.916737</v>
+        <v>27.606768</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>34.383207</v>
+        <v>26.104472</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>32.849676</v>
+        <v>24.602175</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>31.316146</v>
+        <v>23.099879</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>29.782616</v>
+        <v>21.597583</v>
       </c>
     </row>
     <row r="136">
@@ -47170,19 +47122,19 @@
         <v>-0.005</v>
       </c>
       <c r="D136" s="23" t="n">
-        <v>36.066087</v>
+        <v>27.721563</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>34.526179</v>
+        <v>26.21302</v>
       </c>
       <c r="F136" s="23" t="n">
-        <v>32.986272</v>
+        <v>24.704477</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>31.446365</v>
+        <v>23.195933</v>
       </c>
       <c r="H136" s="23" t="n">
-        <v>29.906458</v>
+        <v>21.68739</v>
       </c>
     </row>
     <row r="137">
@@ -47190,19 +47142,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="23" t="n">
-        <v>36.215436</v>
+        <v>27.836358</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>34.669152</v>
+        <v>26.321568</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>33.122869</v>
+        <v>24.806778</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>31.576585</v>
+        <v>23.291988</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>30.030301</v>
+        <v>21.777198</v>
       </c>
     </row>
     <row r="138">
@@ -47210,19 +47162,19 @@
         <v>0.005</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>36.364786</v>
+        <v>27.951153</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>34.812125</v>
+        <v>26.430116</v>
       </c>
       <c r="F138" s="23" t="n">
-        <v>33.259465</v>
+        <v>24.909079</v>
       </c>
       <c r="G138" s="23" t="n">
-        <v>31.706804</v>
+        <v>23.388042</v>
       </c>
       <c r="H138" s="23" t="n">
-        <v>30.154144</v>
+        <v>21.867005</v>
       </c>
     </row>
     <row r="139">
@@ -47230,19 +47182,19 @@
         <v>0.01</v>
       </c>
       <c r="D139" s="23" t="n">
-        <v>36.514136</v>
+        <v>28.065948</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>34.955098</v>
+        <v>26.538664</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>33.396061</v>
+        <v>25.01138</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>31.837024</v>
+        <v>23.484097</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>30.277986</v>
+        <v>21.956813</v>
       </c>
     </row>
   </sheetData>
@@ -51126,7 +51078,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>418.8081705935782</v>
+        <v>418.5930853911187</v>
       </c>
     </row>
     <row r="109">
@@ -51156,7 +51108,7 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>554.7206923963233</v>
+        <v>554.4339121263773</v>
       </c>
     </row>
     <row r="112">
@@ -51339,19 +51291,19 @@
         <v>-0.01</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>552.118124</v>
+        <v>551.8313429999999</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>517.370175</v>
+        <v>517.101319</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>482.622227</v>
+        <v>482.371294</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>447.874279</v>
+        <v>447.64127</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>413.12633</v>
+        <v>412.911245</v>
       </c>
     </row>
     <row r="130">
@@ -51359,19 +51311,19 @@
         <v>-0.005</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>554.507959</v>
+        <v>554.221179</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>519.610646</v>
+        <v>519.3417899999999</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>484.713333</v>
+        <v>484.4624</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>449.81602</v>
+        <v>449.583011</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>414.918707</v>
+        <v>414.703622</v>
       </c>
     </row>
     <row r="131">
@@ -51379,19 +51331,19 @@
         <v>0</v>
       </c>
       <c r="D131" s="23" t="n">
-        <v>556.897795</v>
+        <v>556.611015</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>521.851117</v>
+        <v>521.582261</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>486.804439</v>
+        <v>486.553506</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>451.757761</v>
+        <v>451.524752</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>416.711084</v>
+        <v>416.495998</v>
       </c>
     </row>
     <row r="132">
@@ -51399,19 +51351,19 @@
         <v>0.005</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>559.28763</v>
+        <v>559.00085</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>524.091588</v>
+        <v>523.822731</v>
       </c>
       <c r="F132" s="23" t="n">
-        <v>488.895545</v>
+        <v>488.644613</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>453.699503</v>
+        <v>453.466494</v>
       </c>
       <c r="H132" s="23" t="n">
-        <v>418.50346</v>
+        <v>418.288375</v>
       </c>
     </row>
     <row r="133">
@@ -51419,19 +51371,19 @@
         <v>0.01</v>
       </c>
       <c r="D133" s="23" t="n">
-        <v>561.677466</v>
+        <v>561.390686</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>526.332059</v>
+        <v>526.063202</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>490.986651</v>
+        <v>490.735719</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>455.641244</v>
+        <v>455.408235</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>420.295837</v>
+        <v>420.080752</v>
       </c>
     </row>
   </sheetData>

--- a/models/CONGLOMERATES.xlsx
+++ b/models/CONGLOMERATES.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-31T05:02:47+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-31T09:23:15+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -17473,34 +17473,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="13">
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -21082,7 +21082,7 @@
         </is>
       </c>
       <c r="C100" s="15" t="n">
-        <v>396.089019</v>
+        <v>257.576909</v>
       </c>
     </row>
     <row r="102">
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="C114" s="15" t="n">
-        <v>366.4327653700028</v>
+        <v>277.6106523969429</v>
       </c>
     </row>
     <row r="115">
@@ -21229,7 +21229,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>479.9243028711895</v>
+        <v>346.4940217088107</v>
       </c>
     </row>
     <row r="118">
@@ -21320,19 +21320,19 @@
         <v>-0.01</v>
       </c>
       <c r="D126" s="23" t="n">
-        <v>475.936325</v>
+        <v>343.614796</v>
       </c>
       <c r="E126" s="23" t="n">
-        <v>447.799208</v>
+        <v>326.537052</v>
       </c>
       <c r="F126" s="23" t="n">
-        <v>419.66209</v>
+        <v>309.459307</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>391.524973</v>
+        <v>292.381563</v>
       </c>
       <c r="H126" s="23" t="n">
-        <v>363.387856</v>
+        <v>275.303819</v>
       </c>
     </row>
     <row r="127">
@@ -21340,19 +21340,19 @@
         <v>-0.005</v>
       </c>
       <c r="D127" s="23" t="n">
-        <v>477.930314</v>
+        <v>345.054409</v>
       </c>
       <c r="E127" s="23" t="n">
-        <v>449.675313</v>
+        <v>327.905115</v>
       </c>
       <c r="F127" s="23" t="n">
-        <v>421.420312</v>
+        <v>310.755822</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>393.165312</v>
+        <v>293.606529</v>
       </c>
       <c r="H127" s="23" t="n">
-        <v>364.910311</v>
+        <v>276.457236</v>
       </c>
     </row>
     <row r="128">
@@ -21360,19 +21360,19 @@
         <v>0</v>
       </c>
       <c r="D128" s="23" t="n">
-        <v>479.924303</v>
+        <v>346.494022</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>451.551418</v>
+        <v>329.273179</v>
       </c>
       <c r="F128" s="23" t="n">
-        <v>423.178534</v>
+        <v>312.052337</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>394.80565</v>
+        <v>294.831495</v>
       </c>
       <c r="H128" s="23" t="n">
-        <v>366.432765</v>
+        <v>277.610652</v>
       </c>
     </row>
     <row r="129">
@@ -21380,19 +21380,19 @@
         <v>0.005</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>481.918292</v>
+        <v>347.933635</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>453.427524</v>
+        <v>330.641243</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>424.936756</v>
+        <v>313.348852</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>396.445988</v>
+        <v>296.05646</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>367.95522</v>
+        <v>278.764069</v>
       </c>
     </row>
     <row r="130">
@@ -21400,19 +21400,19 @@
         <v>0.01</v>
       </c>
       <c r="D130" s="23" t="n">
-        <v>483.912281</v>
+        <v>349.373248</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>455.303629</v>
+        <v>332.009307</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>426.694978</v>
+        <v>314.645367</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>398.086326</v>
+        <v>297.281426</v>
       </c>
       <c r="H130" s="23" t="n">
-        <v>369.477674</v>
+        <v>279.917485</v>
       </c>
     </row>
   </sheetData>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>9.343093</v>
+        <v>9.931034</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>0</v>
